--- a/File Sharing/Giga-Ball 2026.xlsx
+++ b/File Sharing/Giga-Ball 2026.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="871">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="974">
   <si>
     <t>Power-Up</t>
   </si>
@@ -1525,6 +1525,9 @@
     <t>Localised Name</t>
   </si>
   <si>
+    <t>Achievement ID</t>
+  </si>
+  <si>
     <t>Point Value</t>
   </si>
   <si>
@@ -1540,7 +1543,7 @@
     <t>Earned Description</t>
   </si>
   <si>
-    <t>Already Exists?</t>
+    <t>Created When</t>
   </si>
   <si>
     <t>Endless Mode 10m</t>
@@ -1549,18 +1552,27 @@
     <t>Endless Mode 10m Milestone</t>
   </si>
   <si>
+    <t>achievementEndlessTen</t>
+  </si>
+  <si>
     <t>Reach 10m in Endless Mode</t>
   </si>
   <si>
     <t>Passed 10m in Endless Mode</t>
   </si>
   <si>
+    <t>Original</t>
+  </si>
+  <si>
     <t>Endless Mode 100m</t>
   </si>
   <si>
     <t>Endless Mode 100m Milestone</t>
   </si>
   <si>
+    <t>achievementEndlessHundred</t>
+  </si>
+  <si>
     <t>Reach 100m in Endless Mode</t>
   </si>
   <si>
@@ -1573,6 +1585,9 @@
     <t>Endless Mode 500m Milestone</t>
   </si>
   <si>
+    <t>achievementEndlessFiveHundred</t>
+  </si>
+  <si>
     <t>Reach 500m in Endless Mode</t>
   </si>
   <si>
@@ -1585,6 +1600,9 @@
     <t>Endless Mode 1,000m Milestone</t>
   </si>
   <si>
+    <t>achievementEndlessOneK</t>
+  </si>
+  <si>
     <t>Reach 1,000m in Endless Mode</t>
   </si>
   <si>
@@ -1597,6 +1615,9 @@
     <t>Endless Mode 5,000m Total Height</t>
   </si>
   <si>
+    <t>achievementEndlessFiveK</t>
+  </si>
+  <si>
     <t>Reach 5,000m Total Height in Endless Mode</t>
   </si>
   <si>
@@ -1609,6 +1630,9 @@
     <t>Endless Mode 10,000m Total Height</t>
   </si>
   <si>
+    <t>achievementEndlessTenK</t>
+  </si>
+  <si>
     <t>Reach 10,000m Total Height in Endless Mode</t>
   </si>
   <si>
@@ -1618,6 +1642,9 @@
     <t>Classic Pack Complete</t>
   </si>
   <si>
+    <t>classicPackComplete</t>
+  </si>
+  <si>
     <t>Complete all levels in Classic Pack</t>
   </si>
   <si>
@@ -1627,6 +1654,9 @@
     <t>Space Pack Complete</t>
   </si>
   <si>
+    <t>spacePackComplete</t>
+  </si>
+  <si>
     <t>Complete all levels in Space Pack</t>
   </si>
   <si>
@@ -1636,24 +1666,33 @@
     <t>Nature Pack Complete</t>
   </si>
   <si>
+    <t>naturePackComplete</t>
+  </si>
+  <si>
     <t>Complete all levels in Nature Pack</t>
   </si>
   <si>
     <t>Passed all levels in Nature Pack</t>
   </si>
   <si>
-    <t>Urban Pack Complete</t>
-  </si>
-  <si>
-    <t>Complete all levels in Urban Pack</t>
-  </si>
-  <si>
-    <t>Passed all levels in Urban Pack</t>
+    <t>City Pack Complete</t>
+  </si>
+  <si>
+    <t>urbanPackComplete</t>
+  </si>
+  <si>
+    <t>Complete all levels in City Pack</t>
+  </si>
+  <si>
+    <t>Passed all levels in City Pack</t>
   </si>
   <si>
     <t>Food Pack Complete</t>
   </si>
   <si>
+    <t>foodPackComplete</t>
+  </si>
+  <si>
     <t>Complete all levels in Food Pack</t>
   </si>
   <si>
@@ -1663,6 +1702,9 @@
     <t>Computer Pack Complete</t>
   </si>
   <si>
+    <t>computerPackComplete</t>
+  </si>
+  <si>
     <t>Complete all levels in Computer Pack</t>
   </si>
   <si>
@@ -1672,6 +1714,9 @@
     <t>Body Pack Complete</t>
   </si>
   <si>
+    <t>bodyPackComplete</t>
+  </si>
+  <si>
     <t>Complete all levels in Body Pack</t>
   </si>
   <si>
@@ -1681,6 +1726,9 @@
     <t>World Pack Complete</t>
   </si>
   <si>
+    <t>worldPackComplete</t>
+  </si>
+  <si>
     <t>Complete all levels in World Pack</t>
   </si>
   <si>
@@ -1690,6 +1738,9 @@
     <t>Emoji Pack Complete</t>
   </si>
   <si>
+    <t>emojiPackComplete</t>
+  </si>
+  <si>
     <t>Complete all levels in Emoji Pack</t>
   </si>
   <si>
@@ -1699,6 +1750,9 @@
     <t>Numbers Pack Complete</t>
   </si>
   <si>
+    <t>numbersPackComplete</t>
+  </si>
+  <si>
     <t>Complete all levels in Numbers Pack</t>
   </si>
   <si>
@@ -1708,6 +1762,9 @@
     <t>Challenge Pack Complete</t>
   </si>
   <si>
+    <t>challengePackComplete</t>
+  </si>
+  <si>
     <t>Complete all levels in Challenge Pack</t>
   </si>
   <si>
@@ -1720,6 +1777,9 @@
     <t>Endless Mode 1 Minute Milestone</t>
   </si>
   <si>
+    <t>endlessOneMins</t>
+  </si>
+  <si>
     <t>Survive 1 minute in Endless Mode</t>
   </si>
   <si>
@@ -1732,6 +1792,9 @@
     <t>Endless Mode 5 Minute Milestone</t>
   </si>
   <si>
+    <t>endlessFiveMins</t>
+  </si>
+  <si>
     <t>Survive 5 minutes in Endless Mode</t>
   </si>
   <si>
@@ -1744,6 +1807,9 @@
     <t>Endless Mode 10 Minute Milestone</t>
   </si>
   <si>
+    <t>endlessTenMins</t>
+  </si>
+  <si>
     <t>Survive 10 minutes in Endless Mode</t>
   </si>
   <si>
@@ -1756,6 +1822,9 @@
     <t>Endless Mode 30 Minute Milestone</t>
   </si>
   <si>
+    <t>endlessThirtyMins</t>
+  </si>
+  <si>
     <t>Survive 30 minutes in Endless Mode</t>
   </si>
   <si>
@@ -1768,6 +1837,9 @@
     <t>Endless Mode 1 Hour Milestone</t>
   </si>
   <si>
+    <t>endlessSixtyMins</t>
+  </si>
+  <si>
     <t>Survive 1 hour in Endless Mode</t>
   </si>
   <si>
@@ -1780,6 +1852,9 @@
     <t>Tidying Up</t>
   </si>
   <si>
+    <t>endlessCleared</t>
+  </si>
+  <si>
     <t>Clear Endless Mode of all active bricks</t>
   </si>
   <si>
@@ -1792,6 +1867,9 @@
     <t>Taking The Plunge</t>
   </si>
   <si>
+    <t>mysteryPowerUp</t>
+  </si>
+  <si>
     <t>Collect Mystery power-up for the first time</t>
   </si>
   <si>
@@ -1804,6 +1882,9 @@
     <t>Now We’re Talking</t>
   </si>
   <si>
+    <t>firstPowerUp</t>
+  </si>
+  <si>
     <t>Collect power-up for the first time</t>
   </si>
   <si>
@@ -1816,6 +1897,9 @@
     <t>Giga-Lasers!</t>
   </si>
   <si>
+    <t>gigaLasers</t>
+  </si>
+  <si>
     <t>Have Giga-Ball and Lasers power-up at the same time</t>
   </si>
   <si>
@@ -1828,6 +1912,9 @@
     <t>Didn’t Even Need It</t>
   </si>
   <si>
+    <t>endBackstop</t>
+  </si>
+  <si>
     <t>End level with Backstop power-up still active</t>
   </si>
   <si>
@@ -1840,6 +1927,9 @@
     <t>That’s My Favourite</t>
   </si>
   <si>
+    <t>favouritePowerUp</t>
+  </si>
+  <si>
     <t>Collect a single power-up 100 times</t>
   </si>
   <si>
@@ -1852,6 +1942,9 @@
     <t>100 And Counting</t>
   </si>
   <si>
+    <t>powerUpCollectorHundred</t>
+  </si>
+  <si>
     <t>Collect 100 power-ups</t>
   </si>
   <si>
@@ -1864,6 +1957,9 @@
     <t>Hoarder</t>
   </si>
   <si>
+    <t>powerUpCollectorThousand</t>
+  </si>
+  <si>
     <t>Collect 1000 power-ups</t>
   </si>
   <si>
@@ -1876,6 +1972,9 @@
     <t>Picky</t>
   </si>
   <si>
+    <t>powerUpLeaverHundred</t>
+  </si>
+  <si>
     <t>Leave 100 power-ups</t>
   </si>
   <si>
@@ -1888,6 +1987,9 @@
     <t>Power-Up Shy</t>
   </si>
   <si>
+    <t>powerUpLeaverThousand</t>
+  </si>
+  <si>
     <t>Leave 1000 power-ups</t>
   </si>
   <si>
@@ -1900,6 +2002,9 @@
     <t>This Is Too Easy</t>
   </si>
   <si>
+    <t>maxPaddleSize</t>
+  </si>
+  <si>
     <t>Expand the paddle to its maximum width</t>
   </si>
   <si>
@@ -1912,6 +2017,9 @@
     <t>Good Luck</t>
   </si>
   <si>
+    <t>minPaddleSize</t>
+  </si>
+  <si>
     <t>Shrink the paddle to its minimum width</t>
   </si>
   <si>
@@ -1924,6 +2032,9 @@
     <t>Beach Ball</t>
   </si>
   <si>
+    <t>maxBallSize</t>
+  </si>
+  <si>
     <t>Expand the ball to its maximum size</t>
   </si>
   <si>
@@ -1936,6 +2047,9 @@
     <t>Pinball</t>
   </si>
   <si>
+    <t>minBallSize</t>
+  </si>
+  <si>
     <t>Shrink the ball to its minimum size</t>
   </si>
   <si>
@@ -1948,6 +2062,9 @@
     <t>Invincible</t>
   </si>
   <si>
+    <t>noBallsLost</t>
+  </si>
+  <si>
     <t>Complete level without losing ball</t>
   </si>
   <si>
@@ -1960,6 +2077,9 @@
     <t>Hanging on</t>
   </si>
   <si>
+    <t>threeBallsLost</t>
+  </si>
+  <si>
     <t>Complete level losing 3 or more balls</t>
   </si>
   <si>
@@ -1972,6 +2092,9 @@
     <t>Super Powers</t>
   </si>
   <si>
+    <t>allLevelPowerUps</t>
+  </si>
+  <si>
     <t>Collect all power-ups on a level</t>
   </si>
   <si>
@@ -1984,6 +2107,9 @@
     <t>Mere Mortal</t>
   </si>
   <si>
+    <t>noLevelPowerUps</t>
+  </si>
+  <si>
     <t>Collect no power-ups on a level</t>
   </si>
   <si>
@@ -1996,6 +2122,9 @@
     <t>Giga-Speedy</t>
   </si>
   <si>
+    <t>quickLevelComplete</t>
+  </si>
+  <si>
     <t>Complete level in under a minute</t>
   </si>
   <si>
@@ -2008,6 +2137,9 @@
     <t>Supreme Paddle Efficiency</t>
   </si>
   <si>
+    <t>fivePaddleHits</t>
+  </si>
+  <si>
     <t>Complete level in 5 or fewer paddle hits</t>
   </si>
   <si>
@@ -2020,6 +2152,9 @@
     <t>Paddle Master</t>
   </si>
   <si>
+    <t>tenPaddleHits</t>
+  </si>
+  <si>
     <t>Complete level in 10 or fewer paddle hits</t>
   </si>
   <si>
@@ -2032,6 +2167,9 @@
     <t>5,000 Points On 1 Level</t>
   </si>
   <si>
+    <t>fiveKPointsLevel</t>
+  </si>
+  <si>
     <t>Collect 5,000 points on a single level</t>
   </si>
   <si>
@@ -2044,6 +2182,9 @@
     <t>10,000 Points On 1 Level</t>
   </si>
   <si>
+    <t>tenKPointsLevel</t>
+  </si>
+  <si>
     <t>Collect 10,000 points on a single level</t>
   </si>
   <si>
@@ -2056,6 +2197,9 @@
     <t>1 Level Down</t>
   </si>
   <si>
+    <t>oneLevelsComplete</t>
+  </si>
+  <si>
     <t>Complete first level</t>
   </si>
   <si>
@@ -2068,6 +2212,9 @@
     <t>Level Decade</t>
   </si>
   <si>
+    <t>tenLevelsComplete</t>
+  </si>
+  <si>
     <t>Complete 10 levels</t>
   </si>
   <si>
@@ -2080,6 +2227,9 @@
     <t>Level Century</t>
   </si>
   <si>
+    <t>hunderdLevelsComplete</t>
+  </si>
+  <si>
     <t>Complete 100 levels</t>
   </si>
   <si>
@@ -2092,6 +2242,9 @@
     <t>Level Millennium</t>
   </si>
   <si>
+    <t>oneKLevelsComplete</t>
+  </si>
+  <si>
     <t>Complete 1,000 levels</t>
   </si>
   <si>
@@ -2104,6 +2257,9 @@
     <t>Level 10 Millenia</t>
   </si>
   <si>
+    <t>tenKLevelsComplete</t>
+  </si>
+  <si>
     <t>Complete 10,000 levels</t>
   </si>
   <si>
@@ -2116,6 +2272,9 @@
     <t>Panic Move</t>
   </si>
   <si>
+    <t>paddleSpeed</t>
+  </si>
+  <si>
     <t>Move the paddle at incredible speeds</t>
   </si>
   <si>
@@ -2128,6 +2287,9 @@
     <t>100,000 And Counting</t>
   </si>
   <si>
+    <t>hundredKTotalScore</t>
+  </si>
+  <si>
     <t>Earn 100,000 total points</t>
   </si>
   <si>
@@ -2140,6 +2302,9 @@
     <t>Half A Mill</t>
   </si>
   <si>
+    <t>fiveHundredKTotalScore</t>
+  </si>
+  <si>
     <t>Earn 500,000 total points</t>
   </si>
   <si>
@@ -2152,6 +2317,9 @@
     <t>Millionaire</t>
   </si>
   <si>
+    <t>millTotalScore</t>
+  </si>
+  <si>
     <t>Earn 1,000,000 total points</t>
   </si>
   <si>
@@ -2164,6 +2332,9 @@
     <t>God-Like</t>
   </si>
   <si>
+    <t>noBallsLostPack</t>
+  </si>
+  <si>
     <t>Complete pack without losing ball</t>
   </si>
   <si>
@@ -2176,6 +2347,9 @@
     <t>More Balls Please</t>
   </si>
   <si>
+    <t>tenBallsLostPack</t>
+  </si>
+  <si>
     <t>Complete pack losing 10 or more balls</t>
   </si>
   <si>
@@ -2188,6 +2362,9 @@
     <t>Super Hero</t>
   </si>
   <si>
+    <t>allPackPowerUps</t>
+  </si>
+  <si>
     <t>Collect all power-ups on a pack</t>
   </si>
   <si>
@@ -2200,6 +2377,9 @@
     <t>Serial Dodger</t>
   </si>
   <si>
+    <t>noPackPowerUps</t>
+  </si>
+  <si>
     <t>Collect no power-ups on a pack</t>
   </si>
   <si>
@@ -2212,6 +2392,9 @@
     <t>And Time</t>
   </si>
   <si>
+    <t>quickPackComplete</t>
+  </si>
+  <si>
     <t>Complete pack in under ten minutes</t>
   </si>
   <si>
@@ -2224,6 +2407,9 @@
     <t>10,000 Points On 1 Pack</t>
   </si>
   <si>
+    <t>tenKPointsPack</t>
+  </si>
+  <si>
     <t>Collect 10,000 points on a single pack</t>
   </si>
   <si>
@@ -2236,6 +2422,9 @@
     <t>25,000 Points On 1 Pack</t>
   </si>
   <si>
+    <t>twoFiveKPointsPack</t>
+  </si>
+  <si>
     <t>Collect 25,000 points on a single pack</t>
   </si>
   <si>
@@ -2248,6 +2437,9 @@
     <t>50,000 Points On 1 Pack</t>
   </si>
   <si>
+    <t>fiftyKPointsPack</t>
+  </si>
+  <si>
     <t>Collect 50,000 points on a single pack</t>
   </si>
   <si>
@@ -2260,6 +2452,9 @@
     <t>1 Pack Down</t>
   </si>
   <si>
+    <t>onePacksComplete</t>
+  </si>
+  <si>
     <t>Complete first pack</t>
   </si>
   <si>
@@ -2272,6 +2467,9 @@
     <t>Pack Decade</t>
   </si>
   <si>
+    <t>tenPacksComplete</t>
+  </si>
+  <si>
     <t>Complete 10 packs</t>
   </si>
   <si>
@@ -2284,6 +2482,9 @@
     <t>Pack Century</t>
   </si>
   <si>
+    <t>hundredPacksComplete</t>
+  </si>
+  <si>
     <t>Complete 100 packs</t>
   </si>
   <si>
@@ -2296,6 +2497,9 @@
     <t>Pack Millennium</t>
   </si>
   <si>
+    <t>thousandPacksComplete</t>
+  </si>
+  <si>
     <t>Complete 1,000 packs</t>
   </si>
   <si>
@@ -2308,6 +2512,9 @@
     <t>Endless Mayhem 10m Milestone</t>
   </si>
   <si>
+    <t>achievementEndlessMayhemTen</t>
+  </si>
+  <si>
     <t>Reach 10m in Endless Mayhem</t>
   </si>
   <si>
@@ -2320,6 +2527,9 @@
     <t>Endless Mayhem 100m Milestone</t>
   </si>
   <si>
+    <t>achievementEndlessMayhemHundred</t>
+  </si>
+  <si>
     <t>Reach 100m in Endless Mayhem</t>
   </si>
   <si>
@@ -2332,6 +2542,9 @@
     <t>Endless Mayhem 500m Milestone</t>
   </si>
   <si>
+    <t>achievementEndlessMayhemFiveHundred</t>
+  </si>
+  <si>
     <t>Reach 500m in Endless Mayhem</t>
   </si>
   <si>
@@ -2344,6 +2557,9 @@
     <t>Endless Mayhem 1,000m Milestone</t>
   </si>
   <si>
+    <t>achievementEndlessMayhemOneK</t>
+  </si>
+  <si>
     <t>Reach 1,000m in Endless Mayhem</t>
   </si>
   <si>
@@ -2356,6 +2572,9 @@
     <t>Endless Mayhem 5,000m Total Height</t>
   </si>
   <si>
+    <t>achievementEndlessMayhemFiveK</t>
+  </si>
+  <si>
     <t>Reach 5,000m Total Height in Endless Mayhem</t>
   </si>
   <si>
@@ -2368,6 +2587,9 @@
     <t>Endless Mayhem 10,000m Total Height</t>
   </si>
   <si>
+    <t>achievementEndlessMayhemTenK</t>
+  </si>
+  <si>
     <t>Reach 10,000m Total Height in Endless Mayhem</t>
   </si>
   <si>
@@ -2380,6 +2602,9 @@
     <t>Endless Mayhem 1 Minute Milestone</t>
   </si>
   <si>
+    <t>mayhemOneMins</t>
+  </si>
+  <si>
     <t>Survive 1 minute in Endless Mayhem</t>
   </si>
   <si>
@@ -2392,6 +2617,9 @@
     <t>Endless Mayhem 5 Minute Milestone</t>
   </si>
   <si>
+    <t>mayhemFiveMins</t>
+  </si>
+  <si>
     <t>Survive 5 minutes in Endless Mayhem</t>
   </si>
   <si>
@@ -2404,6 +2632,9 @@
     <t>Endless Mayhem 10 Minute Milestone</t>
   </si>
   <si>
+    <t>mayhemTenMins</t>
+  </si>
+  <si>
     <t>Survive 10 minutes in Endless Mayhem</t>
   </si>
   <si>
@@ -2416,6 +2647,9 @@
     <t>Endless Mayhem 30 Minute Milestone</t>
   </si>
   <si>
+    <t>mayhemThirtyMins</t>
+  </si>
+  <si>
     <t>Survive 30 minutes in Endless Mayhem</t>
   </si>
   <si>
@@ -2428,6 +2662,9 @@
     <t>Endless Mayhem 1 Hour Milestone</t>
   </si>
   <si>
+    <t>mayhemSixtyMins</t>
+  </si>
+  <si>
     <t>Survive 1 hour in Endless Mayhem</t>
   </si>
   <si>
@@ -2440,6 +2677,9 @@
     <t>Tidying Up Amongst The Mayhem</t>
   </si>
   <si>
+    <t>mayhemClear</t>
+  </si>
+  <si>
     <t>Clear Endless Mayhem of all active bricks</t>
   </si>
   <si>
@@ -2452,12 +2692,24 @@
     <t>Feel The Power Of The Brick</t>
   </si>
   <si>
+    <t>mayhemPowerUpBrick</t>
+  </si>
+  <si>
+    <t>Collect a power-up from a power-up brick</t>
+  </si>
+  <si>
+    <t>Collected a power-up from a power-up brick</t>
+  </si>
+  <si>
     <t>Giga-Wrecking Ball</t>
   </si>
   <si>
     <t>Giga-Wrecking Ball!</t>
   </si>
   <si>
+    <t>mayhemWreckingGiga</t>
+  </si>
+  <si>
     <t>Have Giga-Ball and Wrecking Ball power-up at the same time</t>
   </si>
   <si>
@@ -2470,6 +2722,9 @@
     <t>Juggler</t>
   </si>
   <si>
+    <t>mayhemThreeBalls</t>
+  </si>
+  <si>
     <t>Have 3 balls in play at the same time</t>
   </si>
   <si>
@@ -2482,6 +2737,9 @@
     <t>Wormhole</t>
   </si>
   <si>
+    <t>mayhemPortalTravel</t>
+  </si>
+  <si>
     <t>Have the ball travel between 2 portal bricks</t>
   </si>
   <si>
@@ -2491,6 +2749,12 @@
     <t>Survive Reversed Paddle Control</t>
   </si>
   <si>
+    <t>Paddle Guru</t>
+  </si>
+  <si>
+    <t>mayhemSurviveReversed</t>
+  </si>
+  <si>
     <t>Survive the Reversed Paddle Control power-up</t>
   </si>
   <si>
@@ -2503,6 +2767,9 @@
     <t>Power-Up Completionist</t>
   </si>
   <si>
+    <t>allPowerUpsCollected</t>
+  </si>
+  <si>
     <t>Collect all power-ups at least once</t>
   </si>
   <si>
@@ -2512,6 +2779,9 @@
     <t>Multi-Talented</t>
   </si>
   <si>
+    <t>fivePowerUpsActive</t>
+  </si>
+  <si>
     <t>Have 5 power-ups active at the same time</t>
   </si>
   <si>
@@ -2524,6 +2794,9 @@
     <t>First Daily Challenge</t>
   </si>
   <si>
+    <t>firstDailyChallenge</t>
+  </si>
+  <si>
     <t>Post a score in a Daily Challenge</t>
   </si>
   <si>
@@ -2536,6 +2809,9 @@
     <t>Serial Daily Challenger</t>
   </si>
   <si>
+    <t>tenDailyChallenges</t>
+  </si>
+  <si>
     <t>Completed 10 Daily Challenges</t>
   </si>
   <si>
@@ -2545,6 +2821,9 @@
     <t>Experienced Daily Challenger</t>
   </si>
   <si>
+    <t>hundredDailyChallenges</t>
+  </si>
+  <si>
     <t>Completed 100 Daily Challenges</t>
   </si>
   <si>
@@ -2554,6 +2833,9 @@
     <t>Seasoned Daily Challenger</t>
   </si>
   <si>
+    <t>yearOfDailyChallenges</t>
+  </si>
+  <si>
     <t>Completed 365 Daily Challenges</t>
   </si>
   <si>
@@ -2563,6 +2845,9 @@
     <t>Week Long Streak</t>
   </si>
   <si>
+    <t>dailyWeekStreak</t>
+  </si>
+  <si>
     <t>Complete every Daily Challenge for 1 week</t>
   </si>
   <si>
@@ -2575,6 +2860,9 @@
     <t>Month Long Streak</t>
   </si>
   <si>
+    <t>dailyMonthStreak</t>
+  </si>
+  <si>
     <t>Complete every Daily Challenge for 1 month</t>
   </si>
   <si>
@@ -2587,6 +2875,9 @@
     <t>Year Long Streak</t>
   </si>
   <si>
+    <t>dailyYearStreak</t>
+  </si>
+  <si>
     <t>Complete every Daily Challenge for 1 year</t>
   </si>
   <si>
@@ -2599,6 +2890,9 @@
     <t>Top 10 Finish</t>
   </si>
   <si>
+    <t>dailyTopTen</t>
+  </si>
+  <si>
     <t>Finish in the top 10 of a Daily Challenge</t>
   </si>
   <si>
@@ -2611,6 +2905,9 @@
     <t>Top Of The Charts</t>
   </si>
   <si>
+    <t>dailyFirstPlace</t>
+  </si>
+  <si>
     <t>Finish first in a Daily Challenge</t>
   </si>
   <si>
@@ -2623,6 +2920,9 @@
     <t>Twist Completionist</t>
   </si>
   <si>
+    <t>allTwistsPlayed</t>
+  </si>
+  <si>
     <t>Play a Daily Challenge with each twist at least once</t>
   </si>
   <si>
@@ -2635,6 +2935,9 @@
     <t>Butter Fingers</t>
   </si>
   <si>
+    <t>butterFingers</t>
+  </si>
+  <si>
     <t>Lose the ball before destroying any bricks</t>
   </si>
   <si>
@@ -2644,6 +2947,9 @@
     <t>Blur</t>
   </si>
   <si>
+    <t>maximumBallSpeed</t>
+  </si>
+  <si>
     <t>Accelerate the ball to its maximum speed</t>
   </si>
   <si>
@@ -2654,6 +2960,9 @@
   </si>
   <si>
     <t>Pokey</t>
+  </si>
+  <si>
+    <t>minimumBallSpeed</t>
   </si>
   <si>
     <t>Slow the ball down to its minimum speed</t>
@@ -18127,15 +18436,15 @@
     <tabColor rgb="ff54b94c"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B1:M99"/>
+  <dimension ref="B1:N99"/>
   <sheetFormatPr defaultColWidth="16.3333" defaultRowHeight="19.9" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="1.35156" style="55" customWidth="1"/>
     <col min="2" max="2" width="18.5625" style="55" customWidth="1"/>
-    <col min="3" max="5" width="16.3516" style="55" customWidth="1"/>
-    <col min="6" max="6" width="19.625" style="55" customWidth="1"/>
-    <col min="7" max="13" width="16.3516" style="55" customWidth="1"/>
-    <col min="14" max="16384" width="16.3516" style="55" customWidth="1"/>
+    <col min="3" max="6" width="16.3516" style="55" customWidth="1"/>
+    <col min="7" max="7" width="19.625" style="55" customWidth="1"/>
+    <col min="8" max="14" width="16.3516" style="55" customWidth="1"/>
+    <col min="15" max="16384" width="16.3516" style="55" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="32.25" customHeight="1">
@@ -18160,785 +18469,857 @@
       <c r="H1" t="s" s="35">
         <v>496</v>
       </c>
-      <c r="I1" t="s" s="3">
+      <c r="I1" t="s" s="35">
         <v>497</v>
       </c>
       <c r="J1" t="s" s="3">
+        <v>498</v>
+      </c>
+      <c r="K1" t="s" s="3">
         <v>5</v>
       </c>
-      <c r="K1" t="s" s="3">
+      <c r="L1" t="s" s="3">
         <v>6</v>
       </c>
-      <c r="L1" t="s" s="3">
+      <c r="M1" t="s" s="3">
         <v>7</v>
       </c>
-      <c r="M1" t="s" s="3">
+      <c r="N1" t="s" s="3">
         <v>8</v>
       </c>
     </row>
     <row r="2" ht="32.25" customHeight="1">
       <c r="B2" t="s" s="6">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="C2" t="s" s="6">
-        <v>499</v>
-      </c>
-      <c r="D2" s="7">
+        <v>500</v>
+      </c>
+      <c r="D2" t="s" s="6">
+        <v>501</v>
+      </c>
+      <c r="E2" s="7">
         <v>10</v>
       </c>
-      <c r="E2" t="s" s="6">
-        <v>17</v>
-      </c>
       <c r="F2" t="s" s="6">
         <v>17</v>
       </c>
       <c r="G2" t="s" s="6">
-        <v>500</v>
+        <v>17</v>
       </c>
       <c r="H2" t="s" s="6">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="I2" t="s" s="6">
-        <v>16</v>
-      </c>
-      <c r="J2" s="9"/>
-      <c r="K2" t="s" s="6">
-        <v>16</v>
-      </c>
-      <c r="L2" s="9"/>
+        <v>503</v>
+      </c>
+      <c r="J2" t="s" s="6">
+        <v>504</v>
+      </c>
+      <c r="K2" s="9"/>
+      <c r="L2" t="s" s="6">
+        <v>16</v>
+      </c>
       <c r="M2" s="9"/>
+      <c r="N2" s="9"/>
     </row>
     <row r="3" ht="32.05" customHeight="1">
       <c r="B3" t="s" s="12">
-        <v>502</v>
+        <v>505</v>
       </c>
       <c r="C3" t="s" s="12">
-        <v>503</v>
-      </c>
-      <c r="D3" s="15">
+        <v>506</v>
+      </c>
+      <c r="D3" t="s" s="12">
+        <v>507</v>
+      </c>
+      <c r="E3" s="15">
         <v>10</v>
       </c>
-      <c r="E3" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F3" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G3" t="s" s="12">
+        <v>17</v>
+      </c>
+      <c r="H3" t="s" s="12">
+        <v>508</v>
+      </c>
+      <c r="I3" t="s" s="12">
+        <v>509</v>
+      </c>
+      <c r="J3" t="s" s="12">
         <v>504</v>
       </c>
-      <c r="H3" t="s" s="12">
-        <v>505</v>
-      </c>
-      <c r="I3" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="J3" s="14"/>
-      <c r="K3" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="L3" s="14"/>
+      <c r="K3" s="14"/>
+      <c r="L3" t="s" s="12">
+        <v>16</v>
+      </c>
       <c r="M3" s="14"/>
+      <c r="N3" s="14"/>
     </row>
     <row r="4" ht="32.05" customHeight="1">
       <c r="B4" t="s" s="12">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="C4" t="s" s="12">
-        <v>507</v>
-      </c>
-      <c r="D4" s="15">
+        <v>511</v>
+      </c>
+      <c r="D4" t="s" s="12">
+        <v>512</v>
+      </c>
+      <c r="E4" s="15">
         <v>10</v>
       </c>
-      <c r="E4" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F4" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G4" t="s" s="12">
-        <v>508</v>
+        <v>17</v>
       </c>
       <c r="H4" t="s" s="12">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="I4" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="J4" s="14"/>
-      <c r="K4" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="L4" s="14"/>
+        <v>514</v>
+      </c>
+      <c r="J4" t="s" s="12">
+        <v>504</v>
+      </c>
+      <c r="K4" s="14"/>
+      <c r="L4" t="s" s="12">
+        <v>16</v>
+      </c>
       <c r="M4" s="14"/>
+      <c r="N4" s="14"/>
     </row>
     <row r="5" ht="32.05" customHeight="1">
       <c r="B5" t="s" s="12">
-        <v>510</v>
+        <v>515</v>
       </c>
       <c r="C5" t="s" s="12">
-        <v>511</v>
-      </c>
-      <c r="D5" s="15">
+        <v>516</v>
+      </c>
+      <c r="D5" t="s" s="12">
+        <v>517</v>
+      </c>
+      <c r="E5" s="15">
         <v>10</v>
       </c>
-      <c r="E5" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F5" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G5" t="s" s="12">
-        <v>512</v>
+        <v>17</v>
       </c>
       <c r="H5" t="s" s="12">
-        <v>513</v>
+        <v>518</v>
       </c>
       <c r="I5" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="J5" s="14"/>
-      <c r="K5" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="L5" s="14"/>
+        <v>519</v>
+      </c>
+      <c r="J5" t="s" s="12">
+        <v>504</v>
+      </c>
+      <c r="K5" s="14"/>
+      <c r="L5" t="s" s="12">
+        <v>16</v>
+      </c>
       <c r="M5" s="14"/>
+      <c r="N5" s="14"/>
     </row>
     <row r="6" ht="44.05" customHeight="1">
       <c r="B6" t="s" s="12">
-        <v>514</v>
+        <v>520</v>
       </c>
       <c r="C6" t="s" s="12">
-        <v>515</v>
-      </c>
-      <c r="D6" s="15">
+        <v>521</v>
+      </c>
+      <c r="D6" t="s" s="12">
+        <v>522</v>
+      </c>
+      <c r="E6" s="15">
         <v>10</v>
       </c>
-      <c r="E6" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F6" t="s" s="12">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G6" t="s" s="12">
-        <v>516</v>
+        <v>16</v>
       </c>
       <c r="H6" t="s" s="12">
-        <v>517</v>
+        <v>523</v>
       </c>
       <c r="I6" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="J6" s="14"/>
-      <c r="K6" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="L6" s="14"/>
+        <v>524</v>
+      </c>
+      <c r="J6" t="s" s="12">
+        <v>504</v>
+      </c>
+      <c r="K6" s="14"/>
+      <c r="L6" t="s" s="12">
+        <v>16</v>
+      </c>
       <c r="M6" s="14"/>
+      <c r="N6" s="14"/>
     </row>
     <row r="7" ht="44.05" customHeight="1">
       <c r="B7" t="s" s="12">
-        <v>518</v>
+        <v>525</v>
       </c>
       <c r="C7" t="s" s="12">
-        <v>519</v>
-      </c>
-      <c r="D7" s="15">
+        <v>526</v>
+      </c>
+      <c r="D7" t="s" s="12">
+        <v>527</v>
+      </c>
+      <c r="E7" s="15">
         <v>10</v>
       </c>
-      <c r="E7" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F7" t="s" s="12">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G7" t="s" s="12">
-        <v>520</v>
+        <v>16</v>
       </c>
       <c r="H7" t="s" s="12">
-        <v>521</v>
+        <v>528</v>
       </c>
       <c r="I7" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="J7" s="14"/>
-      <c r="K7" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="L7" s="14"/>
+        <v>529</v>
+      </c>
+      <c r="J7" t="s" s="12">
+        <v>504</v>
+      </c>
+      <c r="K7" s="14"/>
+      <c r="L7" t="s" s="12">
+        <v>16</v>
+      </c>
       <c r="M7" s="14"/>
+      <c r="N7" s="14"/>
     </row>
     <row r="8" ht="32.05" customHeight="1">
       <c r="B8" t="s" s="12">
-        <v>522</v>
+        <v>530</v>
       </c>
       <c r="C8" t="s" s="12">
-        <v>522</v>
-      </c>
-      <c r="D8" s="15">
+        <v>530</v>
+      </c>
+      <c r="D8" t="s" s="12">
+        <v>531</v>
+      </c>
+      <c r="E8" s="15">
         <v>10</v>
       </c>
-      <c r="E8" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F8" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G8" t="s" s="12">
-        <v>523</v>
+        <v>17</v>
       </c>
       <c r="H8" t="s" s="12">
-        <v>524</v>
+        <v>532</v>
       </c>
       <c r="I8" t="s" s="12">
-        <v>16</v>
+        <v>533</v>
       </c>
       <c r="J8" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="K8" s="14"/>
+        <v>504</v>
+      </c>
+      <c r="K8" t="s" s="12">
+        <v>16</v>
+      </c>
       <c r="L8" s="14"/>
       <c r="M8" s="14"/>
+      <c r="N8" s="14"/>
     </row>
     <row r="9" ht="32.05" customHeight="1">
       <c r="B9" t="s" s="12">
-        <v>525</v>
+        <v>534</v>
       </c>
       <c r="C9" t="s" s="12">
-        <v>525</v>
-      </c>
-      <c r="D9" s="15">
+        <v>534</v>
+      </c>
+      <c r="D9" t="s" s="12">
+        <v>535</v>
+      </c>
+      <c r="E9" s="15">
         <v>10</v>
       </c>
-      <c r="E9" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F9" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G9" t="s" s="12">
-        <v>526</v>
+        <v>17</v>
       </c>
       <c r="H9" t="s" s="12">
-        <v>527</v>
+        <v>536</v>
       </c>
       <c r="I9" t="s" s="12">
-        <v>16</v>
+        <v>537</v>
       </c>
       <c r="J9" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="K9" s="14"/>
+        <v>504</v>
+      </c>
+      <c r="K9" t="s" s="12">
+        <v>16</v>
+      </c>
       <c r="L9" s="14"/>
       <c r="M9" s="14"/>
+      <c r="N9" s="14"/>
     </row>
     <row r="10" ht="32.05" customHeight="1">
       <c r="B10" t="s" s="12">
-        <v>528</v>
+        <v>538</v>
       </c>
       <c r="C10" t="s" s="12">
-        <v>528</v>
-      </c>
-      <c r="D10" s="15">
+        <v>538</v>
+      </c>
+      <c r="D10" t="s" s="12">
+        <v>539</v>
+      </c>
+      <c r="E10" s="15">
         <v>10</v>
       </c>
-      <c r="E10" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F10" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G10" t="s" s="12">
-        <v>529</v>
+        <v>17</v>
       </c>
       <c r="H10" t="s" s="12">
-        <v>530</v>
+        <v>540</v>
       </c>
       <c r="I10" t="s" s="12">
-        <v>16</v>
+        <v>541</v>
       </c>
       <c r="J10" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="K10" s="14"/>
+        <v>504</v>
+      </c>
+      <c r="K10" t="s" s="12">
+        <v>16</v>
+      </c>
       <c r="L10" s="14"/>
       <c r="M10" s="14"/>
+      <c r="N10" s="14"/>
     </row>
     <row r="11" ht="32.05" customHeight="1">
       <c r="B11" t="s" s="12">
-        <v>531</v>
+        <v>542</v>
       </c>
       <c r="C11" t="s" s="12">
-        <v>531</v>
-      </c>
-      <c r="D11" s="15">
+        <v>542</v>
+      </c>
+      <c r="D11" t="s" s="12">
+        <v>543</v>
+      </c>
+      <c r="E11" s="15">
         <v>10</v>
       </c>
-      <c r="E11" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F11" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G11" t="s" s="12">
-        <v>532</v>
+        <v>17</v>
       </c>
       <c r="H11" t="s" s="12">
-        <v>533</v>
+        <v>544</v>
       </c>
       <c r="I11" t="s" s="12">
-        <v>16</v>
+        <v>545</v>
       </c>
       <c r="J11" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="K11" s="14"/>
+        <v>504</v>
+      </c>
+      <c r="K11" t="s" s="12">
+        <v>16</v>
+      </c>
       <c r="L11" s="14"/>
       <c r="M11" s="14"/>
+      <c r="N11" s="14"/>
     </row>
     <row r="12" ht="32.05" customHeight="1">
       <c r="B12" t="s" s="12">
-        <v>534</v>
+        <v>546</v>
       </c>
       <c r="C12" t="s" s="12">
-        <v>534</v>
-      </c>
-      <c r="D12" s="15">
+        <v>546</v>
+      </c>
+      <c r="D12" t="s" s="12">
+        <v>547</v>
+      </c>
+      <c r="E12" s="15">
         <v>10</v>
       </c>
-      <c r="E12" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F12" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G12" t="s" s="12">
-        <v>535</v>
+        <v>17</v>
       </c>
       <c r="H12" t="s" s="12">
-        <v>536</v>
+        <v>548</v>
       </c>
       <c r="I12" t="s" s="12">
-        <v>16</v>
+        <v>549</v>
       </c>
       <c r="J12" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="K12" s="14"/>
+        <v>504</v>
+      </c>
+      <c r="K12" t="s" s="12">
+        <v>16</v>
+      </c>
       <c r="L12" s="14"/>
       <c r="M12" s="14"/>
+      <c r="N12" s="14"/>
     </row>
     <row r="13" ht="32.05" customHeight="1">
       <c r="B13" t="s" s="12">
-        <v>537</v>
+        <v>550</v>
       </c>
       <c r="C13" t="s" s="12">
-        <v>537</v>
-      </c>
-      <c r="D13" s="15">
+        <v>550</v>
+      </c>
+      <c r="D13" t="s" s="12">
+        <v>551</v>
+      </c>
+      <c r="E13" s="15">
         <v>10</v>
       </c>
-      <c r="E13" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F13" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G13" t="s" s="12">
-        <v>538</v>
+        <v>17</v>
       </c>
       <c r="H13" t="s" s="12">
-        <v>539</v>
+        <v>552</v>
       </c>
       <c r="I13" t="s" s="12">
-        <v>16</v>
+        <v>553</v>
       </c>
       <c r="J13" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="K13" s="14"/>
+        <v>504</v>
+      </c>
+      <c r="K13" t="s" s="12">
+        <v>16</v>
+      </c>
       <c r="L13" s="14"/>
       <c r="M13" s="14"/>
+      <c r="N13" s="14"/>
     </row>
     <row r="14" ht="32.05" customHeight="1">
       <c r="B14" t="s" s="12">
-        <v>540</v>
+        <v>554</v>
       </c>
       <c r="C14" t="s" s="12">
-        <v>540</v>
-      </c>
-      <c r="D14" s="15">
+        <v>554</v>
+      </c>
+      <c r="D14" t="s" s="12">
+        <v>555</v>
+      </c>
+      <c r="E14" s="15">
         <v>10</v>
       </c>
-      <c r="E14" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F14" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G14" t="s" s="12">
-        <v>541</v>
+        <v>17</v>
       </c>
       <c r="H14" t="s" s="12">
-        <v>542</v>
+        <v>556</v>
       </c>
       <c r="I14" t="s" s="12">
-        <v>16</v>
+        <v>557</v>
       </c>
       <c r="J14" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="K14" s="14"/>
+        <v>504</v>
+      </c>
+      <c r="K14" t="s" s="12">
+        <v>16</v>
+      </c>
       <c r="L14" s="14"/>
       <c r="M14" s="14"/>
+      <c r="N14" s="14"/>
     </row>
     <row r="15" ht="32.05" customHeight="1">
       <c r="B15" t="s" s="12">
-        <v>543</v>
+        <v>558</v>
       </c>
       <c r="C15" t="s" s="12">
-        <v>543</v>
-      </c>
-      <c r="D15" s="15">
+        <v>558</v>
+      </c>
+      <c r="D15" t="s" s="12">
+        <v>559</v>
+      </c>
+      <c r="E15" s="15">
         <v>10</v>
       </c>
-      <c r="E15" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F15" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G15" t="s" s="12">
-        <v>544</v>
+        <v>17</v>
       </c>
       <c r="H15" t="s" s="12">
-        <v>545</v>
+        <v>560</v>
       </c>
       <c r="I15" t="s" s="12">
-        <v>16</v>
+        <v>561</v>
       </c>
       <c r="J15" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="K15" s="14"/>
+        <v>504</v>
+      </c>
+      <c r="K15" t="s" s="12">
+        <v>16</v>
+      </c>
       <c r="L15" s="14"/>
       <c r="M15" s="14"/>
+      <c r="N15" s="14"/>
     </row>
     <row r="16" ht="32.05" customHeight="1">
       <c r="B16" t="s" s="12">
-        <v>546</v>
+        <v>562</v>
       </c>
       <c r="C16" t="s" s="12">
-        <v>546</v>
-      </c>
-      <c r="D16" s="15">
+        <v>562</v>
+      </c>
+      <c r="D16" t="s" s="12">
+        <v>563</v>
+      </c>
+      <c r="E16" s="15">
         <v>10</v>
       </c>
-      <c r="E16" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F16" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G16" t="s" s="12">
-        <v>547</v>
+        <v>17</v>
       </c>
       <c r="H16" t="s" s="12">
-        <v>548</v>
+        <v>564</v>
       </c>
       <c r="I16" t="s" s="12">
-        <v>16</v>
+        <v>565</v>
       </c>
       <c r="J16" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="K16" s="14"/>
+        <v>504</v>
+      </c>
+      <c r="K16" t="s" s="12">
+        <v>16</v>
+      </c>
       <c r="L16" s="14"/>
       <c r="M16" s="14"/>
+      <c r="N16" s="14"/>
     </row>
     <row r="17" ht="32.05" customHeight="1">
       <c r="B17" t="s" s="12">
-        <v>549</v>
+        <v>566</v>
       </c>
       <c r="C17" t="s" s="12">
-        <v>549</v>
-      </c>
-      <c r="D17" s="15">
+        <v>566</v>
+      </c>
+      <c r="D17" t="s" s="12">
+        <v>567</v>
+      </c>
+      <c r="E17" s="15">
         <v>10</v>
       </c>
-      <c r="E17" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F17" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G17" t="s" s="12">
-        <v>550</v>
+        <v>17</v>
       </c>
       <c r="H17" t="s" s="12">
-        <v>551</v>
+        <v>568</v>
       </c>
       <c r="I17" t="s" s="12">
-        <v>16</v>
+        <v>569</v>
       </c>
       <c r="J17" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="K17" s="14"/>
+        <v>504</v>
+      </c>
+      <c r="K17" t="s" s="12">
+        <v>16</v>
+      </c>
       <c r="L17" s="14"/>
       <c r="M17" s="14"/>
+      <c r="N17" s="14"/>
     </row>
     <row r="18" ht="32.05" customHeight="1">
       <c r="B18" t="s" s="12">
-        <v>552</v>
+        <v>570</v>
       </c>
       <c r="C18" t="s" s="12">
-        <v>552</v>
-      </c>
-      <c r="D18" s="15">
+        <v>570</v>
+      </c>
+      <c r="D18" t="s" s="12">
+        <v>571</v>
+      </c>
+      <c r="E18" s="15">
         <v>10</v>
       </c>
-      <c r="E18" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F18" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G18" t="s" s="12">
-        <v>553</v>
+        <v>17</v>
       </c>
       <c r="H18" t="s" s="12">
-        <v>554</v>
+        <v>572</v>
       </c>
       <c r="I18" t="s" s="12">
-        <v>16</v>
+        <v>573</v>
       </c>
       <c r="J18" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="K18" s="14"/>
+        <v>504</v>
+      </c>
+      <c r="K18" t="s" s="12">
+        <v>16</v>
+      </c>
       <c r="L18" s="14"/>
       <c r="M18" s="14"/>
+      <c r="N18" s="14"/>
     </row>
     <row r="19" ht="32.05" customHeight="1">
       <c r="B19" t="s" s="12">
-        <v>555</v>
+        <v>574</v>
       </c>
       <c r="C19" t="s" s="12">
-        <v>556</v>
-      </c>
-      <c r="D19" s="15">
+        <v>575</v>
+      </c>
+      <c r="D19" t="s" s="12">
+        <v>576</v>
+      </c>
+      <c r="E19" s="15">
         <v>10</v>
       </c>
-      <c r="E19" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F19" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G19" t="s" s="12">
-        <v>557</v>
+        <v>17</v>
       </c>
       <c r="H19" t="s" s="12">
-        <v>558</v>
+        <v>577</v>
       </c>
       <c r="I19" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="J19" s="14"/>
-      <c r="K19" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="L19" s="14"/>
+        <v>578</v>
+      </c>
+      <c r="J19" t="s" s="12">
+        <v>504</v>
+      </c>
+      <c r="K19" s="14"/>
+      <c r="L19" t="s" s="12">
+        <v>16</v>
+      </c>
       <c r="M19" s="14"/>
+      <c r="N19" s="14"/>
     </row>
     <row r="20" ht="32.05" customHeight="1">
       <c r="B20" t="s" s="12">
-        <v>559</v>
+        <v>579</v>
       </c>
       <c r="C20" t="s" s="12">
-        <v>560</v>
-      </c>
-      <c r="D20" s="15">
+        <v>580</v>
+      </c>
+      <c r="D20" t="s" s="12">
+        <v>581</v>
+      </c>
+      <c r="E20" s="15">
         <v>10</v>
       </c>
-      <c r="E20" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F20" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G20" t="s" s="12">
-        <v>561</v>
+        <v>17</v>
       </c>
       <c r="H20" t="s" s="12">
-        <v>562</v>
+        <v>582</v>
       </c>
       <c r="I20" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="J20" s="14"/>
-      <c r="K20" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="L20" s="14"/>
+        <v>583</v>
+      </c>
+      <c r="J20" t="s" s="12">
+        <v>504</v>
+      </c>
+      <c r="K20" s="14"/>
+      <c r="L20" t="s" s="12">
+        <v>16</v>
+      </c>
       <c r="M20" s="14"/>
+      <c r="N20" s="14"/>
     </row>
     <row r="21" ht="44.05" customHeight="1">
       <c r="B21" t="s" s="12">
-        <v>563</v>
+        <v>584</v>
       </c>
       <c r="C21" t="s" s="12">
-        <v>564</v>
-      </c>
-      <c r="D21" s="15">
+        <v>585</v>
+      </c>
+      <c r="D21" t="s" s="12">
+        <v>586</v>
+      </c>
+      <c r="E21" s="15">
         <v>10</v>
       </c>
-      <c r="E21" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F21" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G21" t="s" s="12">
-        <v>565</v>
+        <v>17</v>
       </c>
       <c r="H21" t="s" s="12">
-        <v>566</v>
+        <v>587</v>
       </c>
       <c r="I21" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="J21" s="14"/>
-      <c r="K21" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="L21" s="14"/>
+        <v>588</v>
+      </c>
+      <c r="J21" t="s" s="12">
+        <v>504</v>
+      </c>
+      <c r="K21" s="14"/>
+      <c r="L21" t="s" s="12">
+        <v>16</v>
+      </c>
       <c r="M21" s="14"/>
+      <c r="N21" s="14"/>
     </row>
     <row r="22" ht="44.05" customHeight="1">
       <c r="B22" t="s" s="12">
-        <v>567</v>
+        <v>589</v>
       </c>
       <c r="C22" t="s" s="12">
-        <v>568</v>
-      </c>
-      <c r="D22" s="15">
+        <v>590</v>
+      </c>
+      <c r="D22" t="s" s="12">
+        <v>591</v>
+      </c>
+      <c r="E22" s="15">
         <v>10</v>
       </c>
-      <c r="E22" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F22" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G22" t="s" s="12">
-        <v>569</v>
+        <v>17</v>
       </c>
       <c r="H22" t="s" s="12">
-        <v>570</v>
+        <v>592</v>
       </c>
       <c r="I22" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="J22" s="14"/>
-      <c r="K22" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="L22" s="14"/>
+        <v>593</v>
+      </c>
+      <c r="J22" t="s" s="12">
+        <v>504</v>
+      </c>
+      <c r="K22" s="14"/>
+      <c r="L22" t="s" s="12">
+        <v>16</v>
+      </c>
       <c r="M22" s="14"/>
+      <c r="N22" s="14"/>
     </row>
     <row r="23" ht="32.05" customHeight="1">
       <c r="B23" t="s" s="12">
-        <v>571</v>
+        <v>594</v>
       </c>
       <c r="C23" t="s" s="12">
-        <v>572</v>
-      </c>
-      <c r="D23" s="15">
+        <v>595</v>
+      </c>
+      <c r="D23" t="s" s="12">
+        <v>596</v>
+      </c>
+      <c r="E23" s="15">
         <v>10</v>
       </c>
-      <c r="E23" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F23" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G23" t="s" s="12">
-        <v>573</v>
+        <v>17</v>
       </c>
       <c r="H23" t="s" s="12">
-        <v>574</v>
+        <v>597</v>
       </c>
       <c r="I23" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="J23" s="14"/>
-      <c r="K23" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="L23" s="14"/>
+        <v>598</v>
+      </c>
+      <c r="J23" t="s" s="12">
+        <v>504</v>
+      </c>
+      <c r="K23" s="14"/>
+      <c r="L23" t="s" s="12">
+        <v>16</v>
+      </c>
       <c r="M23" s="14"/>
+      <c r="N23" s="14"/>
     </row>
     <row r="24" ht="44.05" customHeight="1">
       <c r="B24" t="s" s="12">
-        <v>575</v>
+        <v>599</v>
       </c>
       <c r="C24" t="s" s="12">
-        <v>576</v>
-      </c>
-      <c r="D24" s="15">
+        <v>600</v>
+      </c>
+      <c r="D24" t="s" s="12">
+        <v>601</v>
+      </c>
+      <c r="E24" s="15">
         <v>10</v>
       </c>
-      <c r="E24" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F24" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G24" t="s" s="12">
-        <v>577</v>
+        <v>17</v>
       </c>
       <c r="H24" t="s" s="12">
-        <v>578</v>
+        <v>602</v>
       </c>
       <c r="I24" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="J24" s="14"/>
-      <c r="K24" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="L24" s="14"/>
+        <v>603</v>
+      </c>
+      <c r="J24" t="s" s="12">
+        <v>504</v>
+      </c>
+      <c r="K24" s="14"/>
+      <c r="L24" t="s" s="12">
+        <v>16</v>
+      </c>
       <c r="M24" s="14"/>
+      <c r="N24" s="14"/>
     </row>
     <row r="25" ht="44.05" customHeight="1">
       <c r="B25" t="s" s="12">
-        <v>579</v>
+        <v>604</v>
       </c>
       <c r="C25" t="s" s="12">
-        <v>580</v>
-      </c>
-      <c r="D25" s="15">
+        <v>605</v>
+      </c>
+      <c r="D25" t="s" s="12">
+        <v>606</v>
+      </c>
+      <c r="E25" s="15">
         <v>10</v>
       </c>
-      <c r="E25" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F25" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G25" t="s" s="12">
-        <v>581</v>
+        <v>17</v>
       </c>
       <c r="H25" t="s" s="12">
-        <v>582</v>
+        <v>607</v>
       </c>
       <c r="I25" t="s" s="12">
-        <v>16</v>
+        <v>608</v>
       </c>
       <c r="J25" t="s" s="12">
-        <v>16</v>
+        <v>504</v>
       </c>
       <c r="K25" t="s" s="12">
         <v>16</v>
@@ -18947,36 +19328,39 @@
         <v>16</v>
       </c>
       <c r="M25" t="s" s="12">
+        <v>16</v>
+      </c>
+      <c r="N25" t="s" s="12">
         <v>16</v>
       </c>
     </row>
     <row r="26" ht="32.05" customHeight="1">
       <c r="B26" t="s" s="12">
-        <v>583</v>
+        <v>609</v>
       </c>
       <c r="C26" t="s" s="12">
-        <v>584</v>
-      </c>
-      <c r="D26" s="15">
+        <v>610</v>
+      </c>
+      <c r="D26" t="s" s="12">
+        <v>611</v>
+      </c>
+      <c r="E26" s="15">
         <v>10</v>
       </c>
-      <c r="E26" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F26" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G26" t="s" s="12">
-        <v>585</v>
+        <v>17</v>
       </c>
       <c r="H26" t="s" s="12">
-        <v>586</v>
+        <v>612</v>
       </c>
       <c r="I26" t="s" s="12">
-        <v>16</v>
+        <v>613</v>
       </c>
       <c r="J26" t="s" s="12">
-        <v>16</v>
+        <v>504</v>
       </c>
       <c r="K26" t="s" s="12">
         <v>16</v>
@@ -18985,36 +19369,39 @@
         <v>16</v>
       </c>
       <c r="M26" t="s" s="12">
+        <v>16</v>
+      </c>
+      <c r="N26" t="s" s="12">
         <v>16</v>
       </c>
     </row>
     <row r="27" ht="44.05" customHeight="1">
       <c r="B27" t="s" s="12">
-        <v>587</v>
+        <v>614</v>
       </c>
       <c r="C27" t="s" s="12">
-        <v>588</v>
-      </c>
-      <c r="D27" s="15">
+        <v>615</v>
+      </c>
+      <c r="D27" t="s" s="12">
+        <v>616</v>
+      </c>
+      <c r="E27" s="15">
         <v>10</v>
       </c>
-      <c r="E27" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F27" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G27" t="s" s="12">
-        <v>589</v>
+        <v>17</v>
       </c>
       <c r="H27" t="s" s="12">
-        <v>590</v>
+        <v>617</v>
       </c>
       <c r="I27" t="s" s="12">
-        <v>16</v>
+        <v>618</v>
       </c>
       <c r="J27" t="s" s="12">
-        <v>16</v>
+        <v>504</v>
       </c>
       <c r="K27" t="s" s="12">
         <v>16</v>
@@ -19023,36 +19410,39 @@
         <v>16</v>
       </c>
       <c r="M27" t="s" s="12">
+        <v>16</v>
+      </c>
+      <c r="N27" t="s" s="12">
         <v>16</v>
       </c>
     </row>
     <row r="28" ht="44.05" customHeight="1">
       <c r="B28" t="s" s="12">
-        <v>591</v>
+        <v>619</v>
       </c>
       <c r="C28" t="s" s="12">
-        <v>592</v>
-      </c>
-      <c r="D28" s="15">
+        <v>620</v>
+      </c>
+      <c r="D28" t="s" s="12">
+        <v>621</v>
+      </c>
+      <c r="E28" s="15">
         <v>10</v>
       </c>
-      <c r="E28" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F28" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G28" t="s" s="12">
-        <v>593</v>
+        <v>17</v>
       </c>
       <c r="H28" t="s" s="12">
-        <v>594</v>
+        <v>622</v>
       </c>
       <c r="I28" t="s" s="12">
-        <v>16</v>
+        <v>623</v>
       </c>
       <c r="J28" t="s" s="12">
-        <v>16</v>
+        <v>504</v>
       </c>
       <c r="K28" t="s" s="12">
         <v>16</v>
@@ -19061,36 +19451,39 @@
         <v>16</v>
       </c>
       <c r="M28" t="s" s="12">
+        <v>16</v>
+      </c>
+      <c r="N28" t="s" s="12">
         <v>16</v>
       </c>
     </row>
     <row r="29" ht="32.05" customHeight="1">
       <c r="B29" t="s" s="12">
-        <v>595</v>
+        <v>624</v>
       </c>
       <c r="C29" t="s" s="12">
-        <v>596</v>
-      </c>
-      <c r="D29" s="15">
+        <v>625</v>
+      </c>
+      <c r="D29" t="s" s="12">
+        <v>626</v>
+      </c>
+      <c r="E29" s="15">
         <v>10</v>
       </c>
-      <c r="E29" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F29" t="s" s="12">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G29" t="s" s="12">
-        <v>597</v>
+        <v>16</v>
       </c>
       <c r="H29" t="s" s="12">
-        <v>598</v>
+        <v>627</v>
       </c>
       <c r="I29" t="s" s="12">
-        <v>16</v>
+        <v>628</v>
       </c>
       <c r="J29" t="s" s="12">
-        <v>16</v>
+        <v>504</v>
       </c>
       <c r="K29" t="s" s="12">
         <v>16</v>
@@ -19099,36 +19492,39 @@
         <v>16</v>
       </c>
       <c r="M29" t="s" s="12">
+        <v>16</v>
+      </c>
+      <c r="N29" t="s" s="12">
         <v>16</v>
       </c>
     </row>
     <row r="30" ht="32.05" customHeight="1">
       <c r="B30" t="s" s="12">
-        <v>599</v>
+        <v>629</v>
       </c>
       <c r="C30" t="s" s="12">
-        <v>600</v>
-      </c>
-      <c r="D30" s="15">
+        <v>630</v>
+      </c>
+      <c r="D30" t="s" s="12">
+        <v>631</v>
+      </c>
+      <c r="E30" s="15">
         <v>10</v>
       </c>
-      <c r="E30" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F30" t="s" s="12">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G30" t="s" s="12">
-        <v>601</v>
+        <v>16</v>
       </c>
       <c r="H30" t="s" s="12">
-        <v>602</v>
+        <v>632</v>
       </c>
       <c r="I30" t="s" s="12">
-        <v>16</v>
+        <v>633</v>
       </c>
       <c r="J30" t="s" s="12">
-        <v>16</v>
+        <v>504</v>
       </c>
       <c r="K30" t="s" s="12">
         <v>16</v>
@@ -19137,36 +19533,39 @@
         <v>16</v>
       </c>
       <c r="M30" t="s" s="12">
+        <v>16</v>
+      </c>
+      <c r="N30" t="s" s="12">
         <v>16</v>
       </c>
     </row>
     <row r="31" ht="32.05" customHeight="1">
       <c r="B31" t="s" s="12">
-        <v>603</v>
+        <v>634</v>
       </c>
       <c r="C31" t="s" s="12">
-        <v>604</v>
-      </c>
-      <c r="D31" s="15">
+        <v>635</v>
+      </c>
+      <c r="D31" t="s" s="12">
+        <v>636</v>
+      </c>
+      <c r="E31" s="15">
         <v>10</v>
       </c>
-      <c r="E31" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F31" t="s" s="12">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G31" t="s" s="12">
-        <v>605</v>
+        <v>16</v>
       </c>
       <c r="H31" t="s" s="12">
-        <v>606</v>
+        <v>637</v>
       </c>
       <c r="I31" t="s" s="12">
-        <v>16</v>
+        <v>638</v>
       </c>
       <c r="J31" t="s" s="12">
-        <v>16</v>
+        <v>504</v>
       </c>
       <c r="K31" t="s" s="12">
         <v>16</v>
@@ -19175,36 +19574,39 @@
         <v>16</v>
       </c>
       <c r="M31" t="s" s="12">
+        <v>16</v>
+      </c>
+      <c r="N31" t="s" s="12">
         <v>16</v>
       </c>
     </row>
     <row r="32" ht="32.05" customHeight="1">
       <c r="B32" t="s" s="12">
-        <v>607</v>
+        <v>639</v>
       </c>
       <c r="C32" t="s" s="12">
-        <v>608</v>
-      </c>
-      <c r="D32" s="15">
+        <v>640</v>
+      </c>
+      <c r="D32" t="s" s="12">
+        <v>641</v>
+      </c>
+      <c r="E32" s="15">
         <v>10</v>
       </c>
-      <c r="E32" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F32" t="s" s="12">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G32" t="s" s="12">
-        <v>609</v>
+        <v>16</v>
       </c>
       <c r="H32" t="s" s="12">
-        <v>610</v>
+        <v>642</v>
       </c>
       <c r="I32" t="s" s="12">
-        <v>16</v>
+        <v>643</v>
       </c>
       <c r="J32" t="s" s="12">
-        <v>16</v>
+        <v>504</v>
       </c>
       <c r="K32" t="s" s="12">
         <v>16</v>
@@ -19213,36 +19615,39 @@
         <v>16</v>
       </c>
       <c r="M32" t="s" s="12">
+        <v>16</v>
+      </c>
+      <c r="N32" t="s" s="12">
         <v>16</v>
       </c>
     </row>
     <row r="33" ht="32.05" customHeight="1">
       <c r="B33" t="s" s="12">
-        <v>611</v>
+        <v>644</v>
       </c>
       <c r="C33" t="s" s="12">
-        <v>612</v>
-      </c>
-      <c r="D33" s="15">
+        <v>645</v>
+      </c>
+      <c r="D33" t="s" s="12">
+        <v>646</v>
+      </c>
+      <c r="E33" s="15">
         <v>10</v>
       </c>
-      <c r="E33" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F33" t="s" s="12">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G33" t="s" s="12">
-        <v>613</v>
+        <v>16</v>
       </c>
       <c r="H33" t="s" s="12">
-        <v>614</v>
+        <v>647</v>
       </c>
       <c r="I33" t="s" s="12">
-        <v>16</v>
+        <v>648</v>
       </c>
       <c r="J33" t="s" s="12">
-        <v>16</v>
+        <v>504</v>
       </c>
       <c r="K33" t="s" s="12">
         <v>16</v>
@@ -19251,36 +19656,39 @@
         <v>16</v>
       </c>
       <c r="M33" t="s" s="12">
+        <v>16</v>
+      </c>
+      <c r="N33" t="s" s="12">
         <v>16</v>
       </c>
     </row>
     <row r="34" ht="44.05" customHeight="1">
       <c r="B34" t="s" s="12">
-        <v>615</v>
+        <v>649</v>
       </c>
       <c r="C34" t="s" s="12">
-        <v>616</v>
-      </c>
-      <c r="D34" s="15">
+        <v>650</v>
+      </c>
+      <c r="D34" t="s" s="12">
+        <v>651</v>
+      </c>
+      <c r="E34" s="15">
         <v>10</v>
       </c>
-      <c r="E34" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F34" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G34" t="s" s="12">
-        <v>617</v>
+        <v>17</v>
       </c>
       <c r="H34" t="s" s="12">
-        <v>618</v>
+        <v>652</v>
       </c>
       <c r="I34" t="s" s="12">
-        <v>16</v>
+        <v>653</v>
       </c>
       <c r="J34" t="s" s="12">
-        <v>16</v>
+        <v>504</v>
       </c>
       <c r="K34" t="s" s="12">
         <v>16</v>
@@ -19289,36 +19697,39 @@
         <v>16</v>
       </c>
       <c r="M34" t="s" s="12">
+        <v>16</v>
+      </c>
+      <c r="N34" t="s" s="12">
         <v>16</v>
       </c>
     </row>
     <row r="35" ht="44.05" customHeight="1">
       <c r="B35" t="s" s="12">
-        <v>619</v>
+        <v>654</v>
       </c>
       <c r="C35" t="s" s="12">
-        <v>620</v>
-      </c>
-      <c r="D35" s="15">
+        <v>655</v>
+      </c>
+      <c r="D35" t="s" s="12">
+        <v>656</v>
+      </c>
+      <c r="E35" s="15">
         <v>10</v>
       </c>
-      <c r="E35" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F35" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G35" t="s" s="12">
-        <v>621</v>
+        <v>17</v>
       </c>
       <c r="H35" t="s" s="12">
-        <v>622</v>
+        <v>657</v>
       </c>
       <c r="I35" t="s" s="12">
-        <v>16</v>
+        <v>658</v>
       </c>
       <c r="J35" t="s" s="12">
-        <v>16</v>
+        <v>504</v>
       </c>
       <c r="K35" t="s" s="12">
         <v>16</v>
@@ -19327,36 +19738,39 @@
         <v>16</v>
       </c>
       <c r="M35" t="s" s="12">
+        <v>16</v>
+      </c>
+      <c r="N35" t="s" s="12">
         <v>16</v>
       </c>
     </row>
     <row r="36" ht="32.05" customHeight="1">
       <c r="B36" t="s" s="12">
-        <v>623</v>
+        <v>659</v>
       </c>
       <c r="C36" t="s" s="12">
-        <v>624</v>
-      </c>
-      <c r="D36" s="15">
+        <v>660</v>
+      </c>
+      <c r="D36" t="s" s="12">
+        <v>661</v>
+      </c>
+      <c r="E36" s="15">
         <v>10</v>
       </c>
-      <c r="E36" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F36" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G36" t="s" s="12">
-        <v>625</v>
+        <v>17</v>
       </c>
       <c r="H36" t="s" s="12">
-        <v>626</v>
+        <v>662</v>
       </c>
       <c r="I36" t="s" s="12">
-        <v>16</v>
+        <v>663</v>
       </c>
       <c r="J36" t="s" s="12">
-        <v>16</v>
+        <v>504</v>
       </c>
       <c r="K36" t="s" s="12">
         <v>16</v>
@@ -19365,36 +19779,39 @@
         <v>16</v>
       </c>
       <c r="M36" t="s" s="12">
+        <v>16</v>
+      </c>
+      <c r="N36" t="s" s="12">
         <v>16</v>
       </c>
     </row>
     <row r="37" ht="32.05" customHeight="1">
       <c r="B37" t="s" s="12">
-        <v>627</v>
+        <v>664</v>
       </c>
       <c r="C37" t="s" s="12">
-        <v>628</v>
-      </c>
-      <c r="D37" s="15">
+        <v>665</v>
+      </c>
+      <c r="D37" t="s" s="12">
+        <v>666</v>
+      </c>
+      <c r="E37" s="15">
         <v>10</v>
       </c>
-      <c r="E37" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F37" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G37" t="s" s="12">
-        <v>629</v>
+        <v>17</v>
       </c>
       <c r="H37" t="s" s="12">
-        <v>630</v>
+        <v>667</v>
       </c>
       <c r="I37" t="s" s="12">
-        <v>16</v>
+        <v>668</v>
       </c>
       <c r="J37" t="s" s="12">
-        <v>16</v>
+        <v>504</v>
       </c>
       <c r="K37" t="s" s="12">
         <v>16</v>
@@ -19403,484 +19820,529 @@
         <v>16</v>
       </c>
       <c r="M37" t="s" s="12">
+        <v>16</v>
+      </c>
+      <c r="N37" t="s" s="12">
         <v>16</v>
       </c>
     </row>
     <row r="38" ht="32.05" customHeight="1">
       <c r="B38" t="s" s="12">
-        <v>631</v>
+        <v>669</v>
       </c>
       <c r="C38" t="s" s="12">
-        <v>632</v>
-      </c>
-      <c r="D38" s="15">
+        <v>670</v>
+      </c>
+      <c r="D38" t="s" s="12">
+        <v>671</v>
+      </c>
+      <c r="E38" s="15">
         <v>10</v>
       </c>
-      <c r="E38" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F38" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G38" t="s" s="12">
-        <v>633</v>
+        <v>17</v>
       </c>
       <c r="H38" t="s" s="12">
-        <v>634</v>
+        <v>672</v>
       </c>
       <c r="I38" t="s" s="12">
-        <v>16</v>
+        <v>673</v>
       </c>
       <c r="J38" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="K38" s="14"/>
+        <v>504</v>
+      </c>
+      <c r="K38" t="s" s="12">
+        <v>16</v>
+      </c>
       <c r="L38" s="14"/>
       <c r="M38" s="14"/>
+      <c r="N38" s="14"/>
     </row>
     <row r="39" ht="44.05" customHeight="1">
       <c r="B39" t="s" s="12">
-        <v>635</v>
+        <v>674</v>
       </c>
       <c r="C39" t="s" s="12">
-        <v>636</v>
-      </c>
-      <c r="D39" s="15">
+        <v>675</v>
+      </c>
+      <c r="D39" t="s" s="12">
+        <v>676</v>
+      </c>
+      <c r="E39" s="15">
         <v>10</v>
       </c>
-      <c r="E39" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F39" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G39" t="s" s="12">
-        <v>637</v>
+        <v>17</v>
       </c>
       <c r="H39" t="s" s="12">
-        <v>638</v>
+        <v>677</v>
       </c>
       <c r="I39" t="s" s="12">
-        <v>16</v>
+        <v>678</v>
       </c>
       <c r="J39" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="K39" s="14"/>
+        <v>504</v>
+      </c>
+      <c r="K39" t="s" s="12">
+        <v>16</v>
+      </c>
       <c r="L39" s="14"/>
       <c r="M39" s="14"/>
+      <c r="N39" s="14"/>
     </row>
     <row r="40" ht="44.05" customHeight="1">
       <c r="B40" t="s" s="12">
-        <v>639</v>
+        <v>679</v>
       </c>
       <c r="C40" t="s" s="12">
-        <v>640</v>
-      </c>
-      <c r="D40" s="15">
+        <v>680</v>
+      </c>
+      <c r="D40" t="s" s="12">
+        <v>681</v>
+      </c>
+      <c r="E40" s="15">
         <v>10</v>
       </c>
-      <c r="E40" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F40" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G40" t="s" s="12">
-        <v>641</v>
+        <v>17</v>
       </c>
       <c r="H40" t="s" s="12">
-        <v>642</v>
+        <v>682</v>
       </c>
       <c r="I40" t="s" s="12">
-        <v>16</v>
+        <v>683</v>
       </c>
       <c r="J40" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="K40" s="14"/>
+        <v>504</v>
+      </c>
+      <c r="K40" t="s" s="12">
+        <v>16</v>
+      </c>
       <c r="L40" s="14"/>
       <c r="M40" s="14"/>
+      <c r="N40" s="14"/>
     </row>
     <row r="41" ht="44.05" customHeight="1">
       <c r="B41" t="s" s="12">
-        <v>643</v>
+        <v>684</v>
       </c>
       <c r="C41" t="s" s="12">
-        <v>644</v>
-      </c>
-      <c r="D41" s="15">
+        <v>685</v>
+      </c>
+      <c r="D41" t="s" s="12">
+        <v>686</v>
+      </c>
+      <c r="E41" s="15">
         <v>10</v>
       </c>
-      <c r="E41" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F41" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G41" t="s" s="12">
-        <v>645</v>
+        <v>17</v>
       </c>
       <c r="H41" t="s" s="12">
-        <v>646</v>
+        <v>687</v>
       </c>
       <c r="I41" t="s" s="12">
-        <v>16</v>
+        <v>688</v>
       </c>
       <c r="J41" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="K41" s="14"/>
+        <v>504</v>
+      </c>
+      <c r="K41" t="s" s="12">
+        <v>16</v>
+      </c>
       <c r="L41" s="14"/>
       <c r="M41" s="14"/>
+      <c r="N41" s="14"/>
     </row>
     <row r="42" ht="32.05" customHeight="1">
       <c r="B42" t="s" s="12">
-        <v>647</v>
+        <v>689</v>
       </c>
       <c r="C42" t="s" s="12">
-        <v>648</v>
-      </c>
-      <c r="D42" s="15">
+        <v>690</v>
+      </c>
+      <c r="D42" t="s" s="12">
+        <v>691</v>
+      </c>
+      <c r="E42" s="15">
         <v>10</v>
       </c>
-      <c r="E42" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F42" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G42" t="s" s="12">
-        <v>649</v>
+        <v>17</v>
       </c>
       <c r="H42" t="s" s="12">
-        <v>650</v>
+        <v>692</v>
       </c>
       <c r="I42" t="s" s="12">
-        <v>16</v>
+        <v>693</v>
       </c>
       <c r="J42" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="K42" s="14"/>
+        <v>504</v>
+      </c>
+      <c r="K42" t="s" s="12">
+        <v>16</v>
+      </c>
       <c r="L42" s="14"/>
       <c r="M42" s="14"/>
+      <c r="N42" s="14"/>
     </row>
     <row r="43" ht="44.05" customHeight="1">
       <c r="B43" t="s" s="12">
-        <v>651</v>
+        <v>694</v>
       </c>
       <c r="C43" t="s" s="12">
-        <v>652</v>
-      </c>
-      <c r="D43" s="15">
+        <v>695</v>
+      </c>
+      <c r="D43" t="s" s="12">
+        <v>696</v>
+      </c>
+      <c r="E43" s="15">
         <v>10</v>
       </c>
-      <c r="E43" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F43" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G43" t="s" s="12">
-        <v>653</v>
+        <v>17</v>
       </c>
       <c r="H43" t="s" s="12">
-        <v>654</v>
+        <v>697</v>
       </c>
       <c r="I43" t="s" s="12">
-        <v>16</v>
+        <v>698</v>
       </c>
       <c r="J43" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="K43" s="14"/>
+        <v>504</v>
+      </c>
+      <c r="K43" t="s" s="12">
+        <v>16</v>
+      </c>
       <c r="L43" s="14"/>
       <c r="M43" s="14"/>
+      <c r="N43" s="14"/>
     </row>
     <row r="44" ht="44.05" customHeight="1">
       <c r="B44" t="s" s="12">
-        <v>655</v>
+        <v>699</v>
       </c>
       <c r="C44" t="s" s="12">
-        <v>656</v>
-      </c>
-      <c r="D44" s="15">
+        <v>700</v>
+      </c>
+      <c r="D44" t="s" s="12">
+        <v>701</v>
+      </c>
+      <c r="E44" s="15">
         <v>10</v>
       </c>
-      <c r="E44" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F44" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G44" t="s" s="12">
-        <v>657</v>
+        <v>17</v>
       </c>
       <c r="H44" t="s" s="12">
-        <v>658</v>
+        <v>702</v>
       </c>
       <c r="I44" t="s" s="12">
-        <v>16</v>
+        <v>703</v>
       </c>
       <c r="J44" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="K44" s="14"/>
+        <v>504</v>
+      </c>
+      <c r="K44" t="s" s="12">
+        <v>16</v>
+      </c>
       <c r="L44" s="14"/>
       <c r="M44" s="14"/>
+      <c r="N44" s="14"/>
     </row>
     <row r="45" ht="44.05" customHeight="1">
       <c r="B45" t="s" s="12">
-        <v>659</v>
+        <v>704</v>
       </c>
       <c r="C45" t="s" s="12">
-        <v>660</v>
-      </c>
-      <c r="D45" s="15">
+        <v>705</v>
+      </c>
+      <c r="D45" t="s" s="12">
+        <v>706</v>
+      </c>
+      <c r="E45" s="15">
         <v>10</v>
       </c>
-      <c r="E45" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F45" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G45" t="s" s="12">
-        <v>661</v>
+        <v>17</v>
       </c>
       <c r="H45" t="s" s="12">
-        <v>662</v>
+        <v>707</v>
       </c>
       <c r="I45" t="s" s="12">
-        <v>16</v>
+        <v>708</v>
       </c>
       <c r="J45" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="K45" s="14"/>
+        <v>504</v>
+      </c>
+      <c r="K45" t="s" s="12">
+        <v>16</v>
+      </c>
       <c r="L45" s="14"/>
       <c r="M45" s="14"/>
+      <c r="N45" s="14"/>
     </row>
     <row r="46" ht="44.05" customHeight="1">
       <c r="B46" t="s" s="12">
-        <v>663</v>
+        <v>709</v>
       </c>
       <c r="C46" t="s" s="12">
-        <v>664</v>
-      </c>
-      <c r="D46" s="15">
+        <v>710</v>
+      </c>
+      <c r="D46" t="s" s="12">
+        <v>711</v>
+      </c>
+      <c r="E46" s="15">
         <v>10</v>
       </c>
-      <c r="E46" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F46" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G46" t="s" s="12">
-        <v>665</v>
+        <v>17</v>
       </c>
       <c r="H46" t="s" s="12">
-        <v>666</v>
+        <v>712</v>
       </c>
       <c r="I46" t="s" s="12">
-        <v>16</v>
+        <v>713</v>
       </c>
       <c r="J46" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="K46" s="14"/>
+        <v>504</v>
+      </c>
+      <c r="K46" t="s" s="12">
+        <v>16</v>
+      </c>
       <c r="L46" s="14"/>
       <c r="M46" s="14"/>
+      <c r="N46" s="14"/>
     </row>
     <row r="47" ht="32.05" customHeight="1">
       <c r="B47" t="s" s="12">
-        <v>667</v>
+        <v>714</v>
       </c>
       <c r="C47" t="s" s="12">
-        <v>668</v>
-      </c>
-      <c r="D47" s="15">
+        <v>715</v>
+      </c>
+      <c r="D47" t="s" s="12">
+        <v>716</v>
+      </c>
+      <c r="E47" s="15">
         <v>10</v>
       </c>
-      <c r="E47" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F47" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G47" t="s" s="12">
-        <v>669</v>
+        <v>17</v>
       </c>
       <c r="H47" t="s" s="12">
-        <v>670</v>
+        <v>717</v>
       </c>
       <c r="I47" t="s" s="12">
-        <v>16</v>
+        <v>718</v>
       </c>
       <c r="J47" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="K47" s="14"/>
+        <v>504</v>
+      </c>
+      <c r="K47" t="s" s="12">
+        <v>16</v>
+      </c>
       <c r="L47" s="14"/>
       <c r="M47" s="14"/>
+      <c r="N47" s="14"/>
     </row>
     <row r="48" ht="32.05" customHeight="1">
       <c r="B48" t="s" s="12">
-        <v>671</v>
+        <v>719</v>
       </c>
       <c r="C48" t="s" s="12">
-        <v>672</v>
-      </c>
-      <c r="D48" s="15">
+        <v>720</v>
+      </c>
+      <c r="D48" t="s" s="12">
+        <v>721</v>
+      </c>
+      <c r="E48" s="15">
         <v>10</v>
       </c>
-      <c r="E48" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F48" t="s" s="12">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G48" t="s" s="12">
-        <v>673</v>
+        <v>16</v>
       </c>
       <c r="H48" t="s" s="12">
-        <v>674</v>
+        <v>722</v>
       </c>
       <c r="I48" t="s" s="12">
-        <v>16</v>
+        <v>723</v>
       </c>
       <c r="J48" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="K48" s="14"/>
+        <v>504</v>
+      </c>
+      <c r="K48" t="s" s="12">
+        <v>16</v>
+      </c>
       <c r="L48" s="14"/>
       <c r="M48" s="14"/>
+      <c r="N48" s="14"/>
     </row>
     <row r="49" ht="32.05" customHeight="1">
       <c r="B49" t="s" s="12">
-        <v>675</v>
+        <v>724</v>
       </c>
       <c r="C49" t="s" s="12">
-        <v>676</v>
-      </c>
-      <c r="D49" s="15">
+        <v>725</v>
+      </c>
+      <c r="D49" t="s" s="12">
+        <v>726</v>
+      </c>
+      <c r="E49" s="15">
         <v>10</v>
       </c>
-      <c r="E49" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F49" t="s" s="12">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G49" t="s" s="12">
-        <v>677</v>
+        <v>16</v>
       </c>
       <c r="H49" t="s" s="12">
-        <v>678</v>
+        <v>727</v>
       </c>
       <c r="I49" t="s" s="12">
-        <v>16</v>
+        <v>728</v>
       </c>
       <c r="J49" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="K49" s="14"/>
+        <v>504</v>
+      </c>
+      <c r="K49" t="s" s="12">
+        <v>16</v>
+      </c>
       <c r="L49" s="14"/>
       <c r="M49" s="14"/>
+      <c r="N49" s="14"/>
     </row>
     <row r="50" ht="32.05" customHeight="1">
       <c r="B50" t="s" s="12">
-        <v>679</v>
+        <v>729</v>
       </c>
       <c r="C50" t="s" s="12">
-        <v>680</v>
-      </c>
-      <c r="D50" s="15">
+        <v>730</v>
+      </c>
+      <c r="D50" t="s" s="12">
+        <v>731</v>
+      </c>
+      <c r="E50" s="15">
         <v>10</v>
       </c>
-      <c r="E50" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F50" t="s" s="12">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G50" t="s" s="12">
-        <v>681</v>
+        <v>16</v>
       </c>
       <c r="H50" t="s" s="12">
-        <v>682</v>
+        <v>732</v>
       </c>
       <c r="I50" t="s" s="12">
-        <v>16</v>
+        <v>733</v>
       </c>
       <c r="J50" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="K50" s="14"/>
+        <v>504</v>
+      </c>
+      <c r="K50" t="s" s="12">
+        <v>16</v>
+      </c>
       <c r="L50" s="14"/>
       <c r="M50" s="14"/>
+      <c r="N50" s="14"/>
     </row>
     <row r="51" ht="32.05" customHeight="1">
       <c r="B51" t="s" s="12">
-        <v>683</v>
+        <v>734</v>
       </c>
       <c r="C51" t="s" s="12">
-        <v>684</v>
-      </c>
-      <c r="D51" s="15">
+        <v>735</v>
+      </c>
+      <c r="D51" t="s" s="12">
+        <v>736</v>
+      </c>
+      <c r="E51" s="15">
         <v>10</v>
       </c>
-      <c r="E51" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F51" t="s" s="12">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G51" t="s" s="12">
-        <v>685</v>
+        <v>16</v>
       </c>
       <c r="H51" t="s" s="12">
-        <v>686</v>
+        <v>737</v>
       </c>
       <c r="I51" t="s" s="12">
-        <v>16</v>
+        <v>738</v>
       </c>
       <c r="J51" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="K51" s="14"/>
+        <v>504</v>
+      </c>
+      <c r="K51" t="s" s="12">
+        <v>16</v>
+      </c>
       <c r="L51" s="14"/>
       <c r="M51" s="14"/>
+      <c r="N51" s="14"/>
     </row>
     <row r="52" ht="32.05" customHeight="1">
       <c r="B52" t="s" s="12">
-        <v>687</v>
+        <v>739</v>
       </c>
       <c r="C52" t="s" s="12">
-        <v>688</v>
-      </c>
-      <c r="D52" s="15">
+        <v>740</v>
+      </c>
+      <c r="D52" t="s" s="12">
+        <v>741</v>
+      </c>
+      <c r="E52" s="15">
         <v>10</v>
       </c>
-      <c r="E52" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F52" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G52" t="s" s="12">
-        <v>689</v>
+        <v>17</v>
       </c>
       <c r="H52" t="s" s="12">
-        <v>690</v>
+        <v>742</v>
       </c>
       <c r="I52" t="s" s="12">
-        <v>16</v>
+        <v>743</v>
       </c>
       <c r="J52" t="s" s="12">
-        <v>16</v>
+        <v>504</v>
       </c>
       <c r="K52" t="s" s="12">
         <v>16</v>
@@ -19889,1064 +20351,1167 @@
         <v>16</v>
       </c>
       <c r="M52" t="s" s="12">
+        <v>16</v>
+      </c>
+      <c r="N52" t="s" s="12">
         <v>16</v>
       </c>
     </row>
     <row r="53" ht="32.05" customHeight="1">
       <c r="B53" t="s" s="12">
-        <v>691</v>
+        <v>744</v>
       </c>
       <c r="C53" t="s" s="12">
-        <v>692</v>
-      </c>
-      <c r="D53" s="15">
+        <v>745</v>
+      </c>
+      <c r="D53" t="s" s="12">
+        <v>746</v>
+      </c>
+      <c r="E53" s="15">
         <v>10</v>
       </c>
-      <c r="E53" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F53" t="s" s="12">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G53" t="s" s="12">
-        <v>693</v>
+        <v>16</v>
       </c>
       <c r="H53" t="s" s="12">
-        <v>694</v>
+        <v>747</v>
       </c>
       <c r="I53" t="s" s="12">
-        <v>16</v>
+        <v>748</v>
       </c>
       <c r="J53" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="K53" s="14"/>
+        <v>504</v>
+      </c>
+      <c r="K53" t="s" s="12">
+        <v>16</v>
+      </c>
       <c r="L53" s="14"/>
       <c r="M53" s="14"/>
+      <c r="N53" s="14"/>
     </row>
     <row r="54" ht="32.05" customHeight="1">
       <c r="B54" t="s" s="12">
-        <v>695</v>
+        <v>749</v>
       </c>
       <c r="C54" t="s" s="12">
-        <v>696</v>
-      </c>
-      <c r="D54" s="15">
+        <v>750</v>
+      </c>
+      <c r="D54" t="s" s="12">
+        <v>751</v>
+      </c>
+      <c r="E54" s="15">
         <v>10</v>
       </c>
-      <c r="E54" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F54" t="s" s="12">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G54" t="s" s="12">
-        <v>697</v>
+        <v>16</v>
       </c>
       <c r="H54" t="s" s="12">
-        <v>698</v>
+        <v>752</v>
       </c>
       <c r="I54" t="s" s="12">
-        <v>16</v>
+        <v>753</v>
       </c>
       <c r="J54" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="K54" s="14"/>
+        <v>504</v>
+      </c>
+      <c r="K54" t="s" s="12">
+        <v>16</v>
+      </c>
       <c r="L54" s="14"/>
       <c r="M54" s="14"/>
+      <c r="N54" s="14"/>
     </row>
     <row r="55" ht="32.05" customHeight="1">
       <c r="B55" t="s" s="12">
-        <v>699</v>
+        <v>754</v>
       </c>
       <c r="C55" t="s" s="12">
-        <v>700</v>
-      </c>
-      <c r="D55" s="15">
+        <v>755</v>
+      </c>
+      <c r="D55" t="s" s="12">
+        <v>756</v>
+      </c>
+      <c r="E55" s="15">
         <v>10</v>
       </c>
-      <c r="E55" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F55" t="s" s="12">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G55" t="s" s="12">
-        <v>701</v>
+        <v>16</v>
       </c>
       <c r="H55" t="s" s="12">
-        <v>702</v>
+        <v>757</v>
       </c>
       <c r="I55" t="s" s="12">
-        <v>16</v>
+        <v>758</v>
       </c>
       <c r="J55" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="K55" s="14"/>
+        <v>504</v>
+      </c>
+      <c r="K55" t="s" s="12">
+        <v>16</v>
+      </c>
       <c r="L55" s="14"/>
       <c r="M55" s="14"/>
+      <c r="N55" s="14"/>
     </row>
     <row r="56" ht="32.05" customHeight="1">
       <c r="B56" t="s" s="12">
-        <v>703</v>
+        <v>759</v>
       </c>
       <c r="C56" t="s" s="12">
-        <v>704</v>
-      </c>
-      <c r="D56" s="15">
+        <v>760</v>
+      </c>
+      <c r="D56" t="s" s="12">
+        <v>761</v>
+      </c>
+      <c r="E56" s="15">
         <v>10</v>
       </c>
-      <c r="E56" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F56" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G56" t="s" s="12">
-        <v>705</v>
+        <v>17</v>
       </c>
       <c r="H56" t="s" s="12">
-        <v>706</v>
+        <v>762</v>
       </c>
       <c r="I56" t="s" s="12">
-        <v>16</v>
+        <v>763</v>
       </c>
       <c r="J56" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="K56" s="14"/>
+        <v>504</v>
+      </c>
+      <c r="K56" t="s" s="12">
+        <v>16</v>
+      </c>
       <c r="L56" s="14"/>
       <c r="M56" s="14"/>
+      <c r="N56" s="14"/>
     </row>
     <row r="57" ht="44.05" customHeight="1">
       <c r="B57" t="s" s="12">
-        <v>707</v>
+        <v>764</v>
       </c>
       <c r="C57" t="s" s="12">
-        <v>708</v>
-      </c>
-      <c r="D57" s="15">
+        <v>765</v>
+      </c>
+      <c r="D57" t="s" s="12">
+        <v>766</v>
+      </c>
+      <c r="E57" s="15">
         <v>10</v>
       </c>
-      <c r="E57" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F57" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G57" t="s" s="12">
-        <v>709</v>
+        <v>17</v>
       </c>
       <c r="H57" t="s" s="12">
-        <v>710</v>
+        <v>767</v>
       </c>
       <c r="I57" t="s" s="12">
-        <v>16</v>
+        <v>768</v>
       </c>
       <c r="J57" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="K57" s="14"/>
+        <v>504</v>
+      </c>
+      <c r="K57" t="s" s="12">
+        <v>16</v>
+      </c>
       <c r="L57" s="14"/>
       <c r="M57" s="14"/>
+      <c r="N57" s="14"/>
     </row>
     <row r="58" ht="44.05" customHeight="1">
       <c r="B58" t="s" s="12">
-        <v>711</v>
+        <v>769</v>
       </c>
       <c r="C58" t="s" s="12">
-        <v>712</v>
-      </c>
-      <c r="D58" s="15">
+        <v>770</v>
+      </c>
+      <c r="D58" t="s" s="12">
+        <v>771</v>
+      </c>
+      <c r="E58" s="15">
         <v>10</v>
       </c>
-      <c r="E58" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F58" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G58" t="s" s="12">
-        <v>713</v>
+        <v>17</v>
       </c>
       <c r="H58" t="s" s="12">
-        <v>714</v>
+        <v>772</v>
       </c>
       <c r="I58" t="s" s="12">
-        <v>16</v>
+        <v>773</v>
       </c>
       <c r="J58" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="K58" s="14"/>
+        <v>504</v>
+      </c>
+      <c r="K58" t="s" s="12">
+        <v>16</v>
+      </c>
       <c r="L58" s="14"/>
       <c r="M58" s="14"/>
+      <c r="N58" s="14"/>
     </row>
     <row r="59" ht="44.05" customHeight="1">
       <c r="B59" t="s" s="12">
-        <v>715</v>
+        <v>774</v>
       </c>
       <c r="C59" t="s" s="12">
-        <v>716</v>
-      </c>
-      <c r="D59" s="15">
+        <v>775</v>
+      </c>
+      <c r="D59" t="s" s="12">
+        <v>776</v>
+      </c>
+      <c r="E59" s="15">
         <v>10</v>
       </c>
-      <c r="E59" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F59" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G59" t="s" s="12">
-        <v>717</v>
+        <v>17</v>
       </c>
       <c r="H59" t="s" s="12">
-        <v>718</v>
+        <v>777</v>
       </c>
       <c r="I59" t="s" s="12">
-        <v>16</v>
+        <v>778</v>
       </c>
       <c r="J59" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="K59" s="14"/>
+        <v>504</v>
+      </c>
+      <c r="K59" t="s" s="12">
+        <v>16</v>
+      </c>
       <c r="L59" s="14"/>
       <c r="M59" s="14"/>
+      <c r="N59" s="14"/>
     </row>
     <row r="60" ht="32.05" customHeight="1">
       <c r="B60" t="s" s="12">
-        <v>719</v>
+        <v>779</v>
       </c>
       <c r="C60" t="s" s="12">
-        <v>720</v>
-      </c>
-      <c r="D60" s="15">
+        <v>780</v>
+      </c>
+      <c r="D60" t="s" s="12">
+        <v>781</v>
+      </c>
+      <c r="E60" s="15">
         <v>10</v>
       </c>
-      <c r="E60" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F60" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G60" t="s" s="12">
-        <v>721</v>
+        <v>17</v>
       </c>
       <c r="H60" t="s" s="12">
-        <v>722</v>
+        <v>782</v>
       </c>
       <c r="I60" t="s" s="12">
-        <v>16</v>
+        <v>783</v>
       </c>
       <c r="J60" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="K60" s="14"/>
+        <v>504</v>
+      </c>
+      <c r="K60" t="s" s="12">
+        <v>16</v>
+      </c>
       <c r="L60" s="14"/>
       <c r="M60" s="14"/>
+      <c r="N60" s="14"/>
     </row>
     <row r="61" ht="44.05" customHeight="1">
       <c r="B61" t="s" s="12">
-        <v>723</v>
+        <v>784</v>
       </c>
       <c r="C61" t="s" s="12">
-        <v>724</v>
-      </c>
-      <c r="D61" s="15">
+        <v>785</v>
+      </c>
+      <c r="D61" t="s" s="12">
+        <v>786</v>
+      </c>
+      <c r="E61" s="15">
         <v>10</v>
       </c>
-      <c r="E61" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F61" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G61" t="s" s="12">
-        <v>725</v>
+        <v>17</v>
       </c>
       <c r="H61" t="s" s="12">
-        <v>726</v>
+        <v>787</v>
       </c>
       <c r="I61" t="s" s="12">
-        <v>16</v>
+        <v>788</v>
       </c>
       <c r="J61" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="K61" s="14"/>
+        <v>504</v>
+      </c>
+      <c r="K61" t="s" s="12">
+        <v>16</v>
+      </c>
       <c r="L61" s="14"/>
       <c r="M61" s="14"/>
+      <c r="N61" s="14"/>
     </row>
     <row r="62" ht="44.05" customHeight="1">
       <c r="B62" t="s" s="12">
-        <v>727</v>
+        <v>789</v>
       </c>
       <c r="C62" t="s" s="12">
-        <v>728</v>
-      </c>
-      <c r="D62" s="15">
+        <v>790</v>
+      </c>
+      <c r="D62" t="s" s="12">
+        <v>791</v>
+      </c>
+      <c r="E62" s="15">
         <v>10</v>
       </c>
-      <c r="E62" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F62" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G62" t="s" s="12">
-        <v>729</v>
+        <v>17</v>
       </c>
       <c r="H62" t="s" s="12">
-        <v>730</v>
+        <v>792</v>
       </c>
       <c r="I62" t="s" s="12">
-        <v>16</v>
+        <v>793</v>
       </c>
       <c r="J62" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="K62" s="14"/>
+        <v>504</v>
+      </c>
+      <c r="K62" t="s" s="12">
+        <v>16</v>
+      </c>
       <c r="L62" s="14"/>
       <c r="M62" s="14"/>
+      <c r="N62" s="14"/>
     </row>
     <row r="63" ht="44.05" customHeight="1">
       <c r="B63" t="s" s="12">
-        <v>731</v>
+        <v>794</v>
       </c>
       <c r="C63" t="s" s="12">
-        <v>732</v>
-      </c>
-      <c r="D63" s="15">
+        <v>795</v>
+      </c>
+      <c r="D63" t="s" s="12">
+        <v>796</v>
+      </c>
+      <c r="E63" s="15">
         <v>10</v>
       </c>
-      <c r="E63" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F63" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G63" t="s" s="12">
-        <v>733</v>
+        <v>17</v>
       </c>
       <c r="H63" t="s" s="12">
-        <v>734</v>
+        <v>797</v>
       </c>
       <c r="I63" t="s" s="12">
-        <v>16</v>
+        <v>798</v>
       </c>
       <c r="J63" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="K63" s="14"/>
+        <v>504</v>
+      </c>
+      <c r="K63" t="s" s="12">
+        <v>16</v>
+      </c>
       <c r="L63" s="14"/>
       <c r="M63" s="14"/>
+      <c r="N63" s="14"/>
     </row>
     <row r="64" ht="32.05" customHeight="1">
       <c r="B64" t="s" s="12">
-        <v>735</v>
+        <v>799</v>
       </c>
       <c r="C64" t="s" s="12">
-        <v>736</v>
-      </c>
-      <c r="D64" s="15">
+        <v>800</v>
+      </c>
+      <c r="D64" t="s" s="12">
+        <v>801</v>
+      </c>
+      <c r="E64" s="15">
         <v>10</v>
       </c>
-      <c r="E64" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F64" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G64" t="s" s="12">
-        <v>737</v>
+        <v>17</v>
       </c>
       <c r="H64" t="s" s="12">
-        <v>738</v>
+        <v>802</v>
       </c>
       <c r="I64" t="s" s="12">
-        <v>16</v>
+        <v>803</v>
       </c>
       <c r="J64" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="K64" s="14"/>
+        <v>504</v>
+      </c>
+      <c r="K64" t="s" s="12">
+        <v>16</v>
+      </c>
       <c r="L64" s="14"/>
       <c r="M64" s="14"/>
+      <c r="N64" s="14"/>
     </row>
     <row r="65" ht="32.05" customHeight="1">
       <c r="B65" t="s" s="12">
-        <v>739</v>
+        <v>804</v>
       </c>
       <c r="C65" t="s" s="12">
-        <v>740</v>
-      </c>
-      <c r="D65" s="15">
+        <v>805</v>
+      </c>
+      <c r="D65" t="s" s="12">
+        <v>806</v>
+      </c>
+      <c r="E65" s="15">
         <v>10</v>
       </c>
-      <c r="E65" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F65" t="s" s="12">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G65" t="s" s="12">
-        <v>741</v>
+        <v>16</v>
       </c>
       <c r="H65" t="s" s="12">
-        <v>742</v>
+        <v>807</v>
       </c>
       <c r="I65" t="s" s="12">
-        <v>16</v>
+        <v>808</v>
       </c>
       <c r="J65" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="K65" s="14"/>
+        <v>504</v>
+      </c>
+      <c r="K65" t="s" s="12">
+        <v>16</v>
+      </c>
       <c r="L65" s="14"/>
       <c r="M65" s="14"/>
+      <c r="N65" s="14"/>
     </row>
     <row r="66" ht="32.05" customHeight="1">
       <c r="B66" t="s" s="12">
-        <v>743</v>
+        <v>809</v>
       </c>
       <c r="C66" t="s" s="12">
-        <v>744</v>
-      </c>
-      <c r="D66" s="15">
+        <v>810</v>
+      </c>
+      <c r="D66" t="s" s="12">
+        <v>811</v>
+      </c>
+      <c r="E66" s="15">
         <v>10</v>
       </c>
-      <c r="E66" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F66" t="s" s="12">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G66" t="s" s="12">
-        <v>745</v>
+        <v>16</v>
       </c>
       <c r="H66" t="s" s="12">
-        <v>746</v>
+        <v>812</v>
       </c>
       <c r="I66" t="s" s="12">
-        <v>16</v>
+        <v>813</v>
       </c>
       <c r="J66" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="K66" s="14"/>
+        <v>504</v>
+      </c>
+      <c r="K66" t="s" s="12">
+        <v>16</v>
+      </c>
       <c r="L66" s="14"/>
       <c r="M66" s="14"/>
+      <c r="N66" s="14"/>
     </row>
     <row r="67" ht="32.05" customHeight="1">
       <c r="B67" t="s" s="12">
-        <v>747</v>
+        <v>814</v>
       </c>
       <c r="C67" t="s" s="12">
-        <v>748</v>
-      </c>
-      <c r="D67" s="15">
+        <v>815</v>
+      </c>
+      <c r="D67" t="s" s="12">
+        <v>816</v>
+      </c>
+      <c r="E67" s="15">
         <v>10</v>
       </c>
-      <c r="E67" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F67" t="s" s="12">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G67" t="s" s="12">
-        <v>749</v>
+        <v>16</v>
       </c>
       <c r="H67" t="s" s="12">
-        <v>750</v>
+        <v>817</v>
       </c>
       <c r="I67" t="s" s="12">
-        <v>16</v>
+        <v>818</v>
       </c>
       <c r="J67" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="K67" s="14"/>
+        <v>504</v>
+      </c>
+      <c r="K67" t="s" s="12">
+        <v>16</v>
+      </c>
       <c r="L67" s="14"/>
       <c r="M67" s="14"/>
+      <c r="N67" s="14"/>
     </row>
     <row r="68" ht="32.05" customHeight="1">
       <c r="B68" t="s" s="12">
-        <v>751</v>
+        <v>819</v>
       </c>
       <c r="C68" t="s" s="12">
-        <v>752</v>
-      </c>
-      <c r="D68" s="15">
+        <v>820</v>
+      </c>
+      <c r="D68" t="s" s="12">
+        <v>821</v>
+      </c>
+      <c r="E68" s="15">
         <v>10</v>
       </c>
-      <c r="E68" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F68" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G68" t="s" s="12">
-        <v>753</v>
+        <v>17</v>
       </c>
       <c r="H68" t="s" s="12">
-        <v>754</v>
+        <v>822</v>
       </c>
       <c r="I68" t="s" s="12">
-        <v>17</v>
-      </c>
-      <c r="J68" s="14"/>
+        <v>823</v>
+      </c>
+      <c r="J68" s="15">
+        <v>1.3</v>
+      </c>
       <c r="K68" s="14"/>
-      <c r="L68" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="M68" s="14"/>
+      <c r="L68" s="14"/>
+      <c r="M68" t="s" s="12">
+        <v>16</v>
+      </c>
+      <c r="N68" s="14"/>
     </row>
     <row r="69" ht="32.05" customHeight="1">
       <c r="B69" t="s" s="12">
-        <v>755</v>
+        <v>824</v>
       </c>
       <c r="C69" t="s" s="12">
-        <v>756</v>
-      </c>
-      <c r="D69" s="15">
+        <v>825</v>
+      </c>
+      <c r="D69" t="s" s="12">
+        <v>826</v>
+      </c>
+      <c r="E69" s="15">
         <v>10</v>
       </c>
-      <c r="E69" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F69" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G69" t="s" s="12">
-        <v>757</v>
+        <v>17</v>
       </c>
       <c r="H69" t="s" s="12">
-        <v>758</v>
+        <v>827</v>
       </c>
       <c r="I69" t="s" s="12">
-        <v>17</v>
-      </c>
-      <c r="J69" s="14"/>
+        <v>828</v>
+      </c>
+      <c r="J69" s="15">
+        <v>1.3</v>
+      </c>
       <c r="K69" s="14"/>
-      <c r="L69" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="M69" s="14"/>
-    </row>
-    <row r="70" ht="32.05" customHeight="1">
+      <c r="L69" s="14"/>
+      <c r="M69" t="s" s="12">
+        <v>16</v>
+      </c>
+      <c r="N69" s="14"/>
+    </row>
+    <row r="70" ht="44.05" customHeight="1">
       <c r="B70" t="s" s="12">
-        <v>759</v>
+        <v>829</v>
       </c>
       <c r="C70" t="s" s="12">
-        <v>760</v>
-      </c>
-      <c r="D70" s="15">
+        <v>830</v>
+      </c>
+      <c r="D70" t="s" s="12">
+        <v>831</v>
+      </c>
+      <c r="E70" s="15">
         <v>10</v>
       </c>
-      <c r="E70" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F70" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G70" t="s" s="12">
-        <v>761</v>
+        <v>17</v>
       </c>
       <c r="H70" t="s" s="12">
-        <v>762</v>
+        <v>832</v>
       </c>
       <c r="I70" t="s" s="12">
-        <v>17</v>
-      </c>
-      <c r="J70" s="14"/>
+        <v>833</v>
+      </c>
+      <c r="J70" s="15">
+        <v>1.3</v>
+      </c>
       <c r="K70" s="14"/>
-      <c r="L70" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="M70" s="14"/>
+      <c r="L70" s="14"/>
+      <c r="M70" t="s" s="12">
+        <v>16</v>
+      </c>
+      <c r="N70" s="14"/>
     </row>
     <row r="71" ht="32.05" customHeight="1">
       <c r="B71" t="s" s="12">
-        <v>763</v>
+        <v>834</v>
       </c>
       <c r="C71" t="s" s="12">
-        <v>764</v>
-      </c>
-      <c r="D71" s="15">
+        <v>835</v>
+      </c>
+      <c r="D71" t="s" s="12">
+        <v>836</v>
+      </c>
+      <c r="E71" s="15">
         <v>10</v>
       </c>
-      <c r="E71" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F71" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G71" t="s" s="12">
-        <v>765</v>
+        <v>17</v>
       </c>
       <c r="H71" t="s" s="12">
-        <v>766</v>
+        <v>837</v>
       </c>
       <c r="I71" t="s" s="12">
-        <v>17</v>
-      </c>
-      <c r="J71" s="14"/>
+        <v>838</v>
+      </c>
+      <c r="J71" s="15">
+        <v>1.3</v>
+      </c>
       <c r="K71" s="14"/>
-      <c r="L71" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="M71" s="14"/>
+      <c r="L71" s="14"/>
+      <c r="M71" t="s" s="12">
+        <v>16</v>
+      </c>
+      <c r="N71" s="14"/>
     </row>
     <row r="72" ht="44.05" customHeight="1">
       <c r="B72" t="s" s="12">
-        <v>767</v>
+        <v>839</v>
       </c>
       <c r="C72" t="s" s="12">
-        <v>768</v>
-      </c>
-      <c r="D72" s="15">
+        <v>840</v>
+      </c>
+      <c r="D72" t="s" s="12">
+        <v>841</v>
+      </c>
+      <c r="E72" s="15">
         <v>10</v>
       </c>
-      <c r="E72" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F72" t="s" s="12">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G72" t="s" s="12">
-        <v>769</v>
+        <v>16</v>
       </c>
       <c r="H72" t="s" s="12">
-        <v>770</v>
+        <v>842</v>
       </c>
       <c r="I72" t="s" s="12">
-        <v>17</v>
-      </c>
-      <c r="J72" s="14"/>
+        <v>843</v>
+      </c>
+      <c r="J72" s="15">
+        <v>1.3</v>
+      </c>
       <c r="K72" s="14"/>
-      <c r="L72" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="M72" s="14"/>
+      <c r="L72" s="14"/>
+      <c r="M72" t="s" s="12">
+        <v>16</v>
+      </c>
+      <c r="N72" s="14"/>
     </row>
     <row r="73" ht="44.05" customHeight="1">
       <c r="B73" t="s" s="12">
-        <v>771</v>
+        <v>844</v>
       </c>
       <c r="C73" t="s" s="12">
-        <v>772</v>
-      </c>
-      <c r="D73" s="15">
+        <v>845</v>
+      </c>
+      <c r="D73" t="s" s="12">
+        <v>846</v>
+      </c>
+      <c r="E73" s="15">
         <v>10</v>
       </c>
-      <c r="E73" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F73" t="s" s="12">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G73" t="s" s="12">
-        <v>773</v>
+        <v>16</v>
       </c>
       <c r="H73" t="s" s="12">
-        <v>774</v>
+        <v>847</v>
       </c>
       <c r="I73" t="s" s="12">
-        <v>17</v>
-      </c>
-      <c r="J73" s="14"/>
+        <v>848</v>
+      </c>
+      <c r="J73" s="15">
+        <v>1.3</v>
+      </c>
       <c r="K73" s="14"/>
-      <c r="L73" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="M73" s="14"/>
+      <c r="L73" s="14"/>
+      <c r="M73" t="s" s="12">
+        <v>16</v>
+      </c>
+      <c r="N73" s="14"/>
     </row>
     <row r="74" ht="32.05" customHeight="1">
       <c r="B74" t="s" s="12">
-        <v>775</v>
+        <v>849</v>
       </c>
       <c r="C74" t="s" s="12">
-        <v>776</v>
-      </c>
-      <c r="D74" s="15">
+        <v>850</v>
+      </c>
+      <c r="D74" t="s" s="12">
+        <v>851</v>
+      </c>
+      <c r="E74" s="15">
         <v>10</v>
       </c>
-      <c r="E74" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F74" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G74" t="s" s="12">
-        <v>777</v>
+        <v>17</v>
       </c>
       <c r="H74" t="s" s="12">
-        <v>778</v>
+        <v>852</v>
       </c>
       <c r="I74" t="s" s="12">
-        <v>17</v>
-      </c>
-      <c r="J74" s="14"/>
+        <v>853</v>
+      </c>
+      <c r="J74" s="15">
+        <v>1.3</v>
+      </c>
       <c r="K74" s="14"/>
-      <c r="L74" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="M74" s="14"/>
+      <c r="L74" s="14"/>
+      <c r="M74" t="s" s="12">
+        <v>16</v>
+      </c>
+      <c r="N74" s="14"/>
     </row>
     <row r="75" ht="32.05" customHeight="1">
       <c r="B75" t="s" s="12">
-        <v>779</v>
+        <v>854</v>
       </c>
       <c r="C75" t="s" s="12">
-        <v>780</v>
-      </c>
-      <c r="D75" s="15">
+        <v>855</v>
+      </c>
+      <c r="D75" t="s" s="12">
+        <v>856</v>
+      </c>
+      <c r="E75" s="15">
         <v>10</v>
       </c>
-      <c r="E75" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F75" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G75" t="s" s="12">
-        <v>781</v>
+        <v>17</v>
       </c>
       <c r="H75" t="s" s="12">
-        <v>782</v>
+        <v>857</v>
       </c>
       <c r="I75" t="s" s="12">
-        <v>17</v>
-      </c>
-      <c r="J75" s="14"/>
+        <v>858</v>
+      </c>
+      <c r="J75" s="15">
+        <v>1.3</v>
+      </c>
       <c r="K75" s="14"/>
-      <c r="L75" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="M75" s="14"/>
+      <c r="L75" s="14"/>
+      <c r="M75" t="s" s="12">
+        <v>16</v>
+      </c>
+      <c r="N75" s="14"/>
     </row>
     <row r="76" ht="44.05" customHeight="1">
       <c r="B76" t="s" s="12">
-        <v>783</v>
+        <v>859</v>
       </c>
       <c r="C76" t="s" s="12">
-        <v>784</v>
-      </c>
-      <c r="D76" s="15">
+        <v>860</v>
+      </c>
+      <c r="D76" t="s" s="12">
+        <v>861</v>
+      </c>
+      <c r="E76" s="15">
         <v>10</v>
       </c>
-      <c r="E76" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F76" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G76" t="s" s="12">
-        <v>785</v>
+        <v>17</v>
       </c>
       <c r="H76" t="s" s="12">
-        <v>786</v>
+        <v>862</v>
       </c>
       <c r="I76" t="s" s="12">
-        <v>17</v>
-      </c>
-      <c r="J76" s="14"/>
+        <v>863</v>
+      </c>
+      <c r="J76" s="15">
+        <v>1.3</v>
+      </c>
       <c r="K76" s="14"/>
-      <c r="L76" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="M76" s="14"/>
+      <c r="L76" s="14"/>
+      <c r="M76" t="s" s="12">
+        <v>16</v>
+      </c>
+      <c r="N76" s="14"/>
     </row>
     <row r="77" ht="44.05" customHeight="1">
       <c r="B77" t="s" s="12">
-        <v>787</v>
+        <v>864</v>
       </c>
       <c r="C77" t="s" s="12">
-        <v>788</v>
-      </c>
-      <c r="D77" s="15">
+        <v>865</v>
+      </c>
+      <c r="D77" t="s" s="12">
+        <v>866</v>
+      </c>
+      <c r="E77" s="15">
         <v>10</v>
       </c>
-      <c r="E77" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F77" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G77" t="s" s="12">
-        <v>789</v>
+        <v>17</v>
       </c>
       <c r="H77" t="s" s="12">
-        <v>790</v>
+        <v>867</v>
       </c>
       <c r="I77" t="s" s="12">
-        <v>17</v>
-      </c>
-      <c r="J77" s="14"/>
+        <v>868</v>
+      </c>
+      <c r="J77" s="15">
+        <v>1.3</v>
+      </c>
       <c r="K77" s="14"/>
-      <c r="L77" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="M77" s="14"/>
+      <c r="L77" s="14"/>
+      <c r="M77" t="s" s="12">
+        <v>16</v>
+      </c>
+      <c r="N77" s="14"/>
     </row>
     <row r="78" ht="32.05" customHeight="1">
       <c r="B78" t="s" s="12">
-        <v>791</v>
+        <v>869</v>
       </c>
       <c r="C78" t="s" s="12">
-        <v>792</v>
-      </c>
-      <c r="D78" s="15">
+        <v>870</v>
+      </c>
+      <c r="D78" t="s" s="12">
+        <v>871</v>
+      </c>
+      <c r="E78" s="15">
         <v>10</v>
       </c>
-      <c r="E78" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F78" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G78" t="s" s="12">
-        <v>793</v>
+        <v>17</v>
       </c>
       <c r="H78" t="s" s="12">
-        <v>794</v>
+        <v>872</v>
       </c>
       <c r="I78" t="s" s="12">
-        <v>17</v>
-      </c>
-      <c r="J78" s="14"/>
+        <v>873</v>
+      </c>
+      <c r="J78" s="15">
+        <v>1.3</v>
+      </c>
       <c r="K78" s="14"/>
-      <c r="L78" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="M78" s="14"/>
+      <c r="L78" s="14"/>
+      <c r="M78" t="s" s="12">
+        <v>16</v>
+      </c>
+      <c r="N78" s="14"/>
     </row>
     <row r="79" ht="44.05" customHeight="1">
       <c r="B79" t="s" s="12">
-        <v>795</v>
+        <v>874</v>
       </c>
       <c r="C79" t="s" s="12">
-        <v>796</v>
-      </c>
-      <c r="D79" s="15">
+        <v>875</v>
+      </c>
+      <c r="D79" t="s" s="12">
+        <v>876</v>
+      </c>
+      <c r="E79" s="15">
         <v>10</v>
       </c>
-      <c r="E79" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F79" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G79" t="s" s="12">
-        <v>797</v>
+        <v>17</v>
       </c>
       <c r="H79" t="s" s="12">
-        <v>798</v>
+        <v>877</v>
       </c>
       <c r="I79" t="s" s="12">
-        <v>17</v>
-      </c>
-      <c r="J79" s="14"/>
+        <v>878</v>
+      </c>
+      <c r="J79" s="15">
+        <v>1.3</v>
+      </c>
       <c r="K79" s="14"/>
-      <c r="L79" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="M79" s="14"/>
+      <c r="L79" s="14"/>
+      <c r="M79" t="s" s="12">
+        <v>16</v>
+      </c>
+      <c r="N79" s="14"/>
     </row>
     <row r="80" ht="44.05" customHeight="1">
       <c r="B80" t="s" s="12">
-        <v>799</v>
+        <v>879</v>
       </c>
       <c r="C80" t="s" s="12">
-        <v>800</v>
-      </c>
-      <c r="D80" s="15">
+        <v>880</v>
+      </c>
+      <c r="D80" t="s" s="12">
+        <v>881</v>
+      </c>
+      <c r="E80" s="15">
         <v>10</v>
       </c>
-      <c r="E80" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F80" t="s" s="12">
         <v>17</v>
       </c>
-      <c r="G80" s="14"/>
-      <c r="H80" s="14"/>
+      <c r="G80" t="s" s="12">
+        <v>17</v>
+      </c>
+      <c r="H80" t="s" s="12">
+        <v>882</v>
+      </c>
       <c r="I80" t="s" s="12">
-        <v>17</v>
-      </c>
-      <c r="J80" s="14"/>
+        <v>883</v>
+      </c>
+      <c r="J80" s="15">
+        <v>1.3</v>
+      </c>
       <c r="K80" s="14"/>
-      <c r="L80" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="M80" s="14"/>
+      <c r="L80" s="14"/>
+      <c r="M80" t="s" s="12">
+        <v>16</v>
+      </c>
+      <c r="N80" s="14"/>
     </row>
     <row r="81" ht="56.05" customHeight="1">
       <c r="B81" t="s" s="12">
-        <v>801</v>
+        <v>884</v>
       </c>
       <c r="C81" t="s" s="12">
-        <v>802</v>
-      </c>
-      <c r="D81" s="15">
+        <v>885</v>
+      </c>
+      <c r="D81" t="s" s="12">
+        <v>886</v>
+      </c>
+      <c r="E81" s="15">
         <v>10</v>
       </c>
-      <c r="E81" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F81" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G81" t="s" s="12">
-        <v>803</v>
+        <v>17</v>
       </c>
       <c r="H81" t="s" s="12">
-        <v>804</v>
+        <v>887</v>
       </c>
       <c r="I81" t="s" s="12">
-        <v>17</v>
-      </c>
-      <c r="J81" s="14"/>
+        <v>888</v>
+      </c>
+      <c r="J81" s="15">
+        <v>1.3</v>
+      </c>
       <c r="K81" s="14"/>
-      <c r="L81" t="s" s="12">
-        <v>16</v>
-      </c>
+      <c r="L81" s="14"/>
       <c r="M81" t="s" s="12">
+        <v>16</v>
+      </c>
+      <c r="N81" t="s" s="12">
         <v>16</v>
       </c>
     </row>
     <row r="82" ht="32.05" customHeight="1">
       <c r="B82" t="s" s="12">
-        <v>805</v>
+        <v>889</v>
       </c>
       <c r="C82" t="s" s="12">
-        <v>806</v>
-      </c>
-      <c r="D82" s="15">
+        <v>890</v>
+      </c>
+      <c r="D82" t="s" s="12">
+        <v>891</v>
+      </c>
+      <c r="E82" s="15">
         <v>10</v>
       </c>
-      <c r="E82" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F82" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G82" t="s" s="12">
-        <v>807</v>
+        <v>17</v>
       </c>
       <c r="H82" t="s" s="12">
-        <v>808</v>
+        <v>892</v>
       </c>
       <c r="I82" t="s" s="12">
-        <v>17</v>
-      </c>
-      <c r="J82" s="14"/>
+        <v>893</v>
+      </c>
+      <c r="J82" s="15">
+        <v>1.3</v>
+      </c>
       <c r="K82" s="14"/>
-      <c r="L82" t="s" s="12">
-        <v>16</v>
-      </c>
+      <c r="L82" s="14"/>
       <c r="M82" t="s" s="12">
+        <v>16</v>
+      </c>
+      <c r="N82" t="s" s="12">
         <v>16</v>
       </c>
     </row>
     <row r="83" ht="44.05" customHeight="1">
       <c r="B83" t="s" s="12">
-        <v>809</v>
+        <v>894</v>
       </c>
       <c r="C83" t="s" s="12">
-        <v>810</v>
-      </c>
-      <c r="D83" s="15">
+        <v>895</v>
+      </c>
+      <c r="D83" t="s" s="12">
+        <v>896</v>
+      </c>
+      <c r="E83" s="15">
         <v>10</v>
       </c>
-      <c r="E83" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F83" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G83" t="s" s="12">
-        <v>811</v>
+        <v>17</v>
       </c>
       <c r="H83" t="s" s="12">
-        <v>812</v>
+        <v>897</v>
       </c>
       <c r="I83" t="s" s="12">
-        <v>17</v>
-      </c>
-      <c r="J83" s="14"/>
+        <v>898</v>
+      </c>
+      <c r="J83" s="15">
+        <v>1.3</v>
+      </c>
       <c r="K83" s="14"/>
-      <c r="L83" t="s" s="12">
-        <v>16</v>
-      </c>
+      <c r="L83" s="14"/>
       <c r="M83" t="s" s="12">
+        <v>16</v>
+      </c>
+      <c r="N83" t="s" s="12">
         <v>16</v>
       </c>
     </row>
     <row r="84" ht="44.05" customHeight="1">
       <c r="B84" t="s" s="12">
-        <v>813</v>
+        <v>899</v>
       </c>
       <c r="C84" t="s" s="12">
-        <v>656</v>
-      </c>
-      <c r="D84" s="15">
+        <v>900</v>
+      </c>
+      <c r="D84" t="s" s="12">
+        <v>901</v>
+      </c>
+      <c r="E84" s="15">
         <v>10</v>
       </c>
-      <c r="E84" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F84" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G84" t="s" s="12">
-        <v>814</v>
+        <v>17</v>
       </c>
       <c r="H84" t="s" s="12">
-        <v>815</v>
+        <v>902</v>
       </c>
       <c r="I84" t="s" s="12">
-        <v>17</v>
-      </c>
-      <c r="J84" s="14"/>
+        <v>903</v>
+      </c>
+      <c r="J84" s="15">
+        <v>1.3</v>
+      </c>
       <c r="K84" s="14"/>
-      <c r="L84" t="s" s="12">
-        <v>16</v>
-      </c>
+      <c r="L84" s="14"/>
       <c r="M84" t="s" s="12">
+        <v>16</v>
+      </c>
+      <c r="N84" t="s" s="12">
         <v>16</v>
       </c>
     </row>
     <row r="85" ht="32.05" customHeight="1">
       <c r="B85" t="s" s="12">
-        <v>816</v>
+        <v>904</v>
       </c>
       <c r="C85" t="s" s="12">
-        <v>817</v>
-      </c>
-      <c r="D85" s="15">
+        <v>905</v>
+      </c>
+      <c r="D85" t="s" s="12">
+        <v>906</v>
+      </c>
+      <c r="E85" s="15">
         <v>10</v>
       </c>
-      <c r="E85" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F85" t="s" s="12">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G85" t="s" s="12">
-        <v>818</v>
+        <v>16</v>
       </c>
       <c r="H85" t="s" s="12">
-        <v>818</v>
+        <v>907</v>
       </c>
       <c r="I85" t="s" s="12">
-        <v>17</v>
-      </c>
-      <c r="J85" t="s" s="12">
-        <v>16</v>
+        <v>907</v>
+      </c>
+      <c r="J85" s="15">
+        <v>1.3</v>
       </c>
       <c r="K85" t="s" s="12">
         <v>16</v>
@@ -20955,36 +21520,39 @@
         <v>16</v>
       </c>
       <c r="M85" t="s" s="12">
+        <v>16</v>
+      </c>
+      <c r="N85" t="s" s="12">
         <v>16</v>
       </c>
     </row>
     <row r="86" ht="44.05" customHeight="1">
       <c r="B86" t="s" s="12">
-        <v>819</v>
+        <v>908</v>
       </c>
       <c r="C86" t="s" s="12">
-        <v>820</v>
-      </c>
-      <c r="D86" s="15">
+        <v>909</v>
+      </c>
+      <c r="D86" t="s" s="12">
+        <v>910</v>
+      </c>
+      <c r="E86" s="15">
         <v>10</v>
       </c>
-      <c r="E86" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F86" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G86" t="s" s="12">
-        <v>821</v>
+        <v>17</v>
       </c>
       <c r="H86" t="s" s="12">
-        <v>822</v>
+        <v>911</v>
       </c>
       <c r="I86" t="s" s="12">
-        <v>17</v>
-      </c>
-      <c r="J86" t="s" s="12">
-        <v>16</v>
+        <v>912</v>
+      </c>
+      <c r="J86" s="15">
+        <v>1.3</v>
       </c>
       <c r="K86" t="s" s="12">
         <v>16</v>
@@ -20993,36 +21561,39 @@
         <v>16</v>
       </c>
       <c r="M86" t="s" s="12">
+        <v>16</v>
+      </c>
+      <c r="N86" t="s" s="12">
         <v>16</v>
       </c>
     </row>
     <row r="87" ht="32.05" customHeight="1">
       <c r="B87" t="s" s="12">
-        <v>823</v>
+        <v>913</v>
       </c>
       <c r="C87" t="s" s="12">
-        <v>824</v>
-      </c>
-      <c r="D87" s="15">
+        <v>914</v>
+      </c>
+      <c r="D87" t="s" s="12">
+        <v>915</v>
+      </c>
+      <c r="E87" s="15">
         <v>10</v>
       </c>
-      <c r="E87" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F87" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G87" t="s" s="12">
-        <v>825</v>
+        <v>17</v>
       </c>
       <c r="H87" t="s" s="12">
-        <v>826</v>
+        <v>916</v>
       </c>
       <c r="I87" t="s" s="12">
-        <v>17</v>
-      </c>
-      <c r="J87" t="s" s="12">
-        <v>16</v>
+        <v>917</v>
+      </c>
+      <c r="J87" s="15">
+        <v>1.3</v>
       </c>
       <c r="K87" t="s" s="12">
         <v>16</v>
@@ -21031,36 +21602,39 @@
         <v>16</v>
       </c>
       <c r="M87" t="s" s="12">
+        <v>16</v>
+      </c>
+      <c r="N87" t="s" s="12">
         <v>16</v>
       </c>
     </row>
     <row r="88" ht="32.05" customHeight="1">
       <c r="B88" t="s" s="12">
-        <v>827</v>
+        <v>918</v>
       </c>
       <c r="C88" t="s" s="12">
-        <v>828</v>
-      </c>
-      <c r="D88" s="15">
+        <v>919</v>
+      </c>
+      <c r="D88" t="s" s="12">
+        <v>920</v>
+      </c>
+      <c r="E88" s="15">
         <v>10</v>
       </c>
-      <c r="E88" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F88" t="s" s="12">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G88" t="s" s="12">
-        <v>827</v>
+        <v>16</v>
       </c>
       <c r="H88" t="s" s="12">
-        <v>829</v>
+        <v>918</v>
       </c>
       <c r="I88" t="s" s="12">
-        <v>17</v>
-      </c>
-      <c r="J88" t="s" s="12">
-        <v>16</v>
+        <v>921</v>
+      </c>
+      <c r="J88" s="15">
+        <v>1.3</v>
       </c>
       <c r="K88" t="s" s="12">
         <v>16</v>
@@ -21069,36 +21643,39 @@
         <v>16</v>
       </c>
       <c r="M88" t="s" s="12">
+        <v>16</v>
+      </c>
+      <c r="N88" t="s" s="12">
         <v>16</v>
       </c>
     </row>
     <row r="89" ht="32.05" customHeight="1">
       <c r="B89" t="s" s="12">
-        <v>830</v>
+        <v>922</v>
       </c>
       <c r="C89" t="s" s="12">
-        <v>831</v>
-      </c>
-      <c r="D89" s="15">
+        <v>923</v>
+      </c>
+      <c r="D89" t="s" s="12">
+        <v>924</v>
+      </c>
+      <c r="E89" s="15">
         <v>10</v>
       </c>
-      <c r="E89" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F89" t="s" s="12">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G89" t="s" s="12">
-        <v>830</v>
+        <v>16</v>
       </c>
       <c r="H89" t="s" s="12">
-        <v>832</v>
+        <v>922</v>
       </c>
       <c r="I89" t="s" s="12">
-        <v>17</v>
-      </c>
-      <c r="J89" t="s" s="12">
-        <v>16</v>
+        <v>925</v>
+      </c>
+      <c r="J89" s="15">
+        <v>1.3</v>
       </c>
       <c r="K89" t="s" s="12">
         <v>16</v>
@@ -21107,36 +21684,39 @@
         <v>16</v>
       </c>
       <c r="M89" t="s" s="12">
+        <v>16</v>
+      </c>
+      <c r="N89" t="s" s="12">
         <v>16</v>
       </c>
     </row>
     <row r="90" ht="32.05" customHeight="1">
       <c r="B90" t="s" s="12">
-        <v>833</v>
+        <v>926</v>
       </c>
       <c r="C90" t="s" s="12">
-        <v>834</v>
-      </c>
-      <c r="D90" s="15">
+        <v>927</v>
+      </c>
+      <c r="D90" t="s" s="12">
+        <v>928</v>
+      </c>
+      <c r="E90" s="15">
         <v>10</v>
       </c>
-      <c r="E90" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F90" t="s" s="12">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G90" t="s" s="12">
-        <v>833</v>
+        <v>16</v>
       </c>
       <c r="H90" t="s" s="12">
-        <v>835</v>
+        <v>926</v>
       </c>
       <c r="I90" t="s" s="12">
-        <v>17</v>
-      </c>
-      <c r="J90" t="s" s="12">
-        <v>16</v>
+        <v>929</v>
+      </c>
+      <c r="J90" s="15">
+        <v>1.3</v>
       </c>
       <c r="K90" t="s" s="12">
         <v>16</v>
@@ -21145,36 +21725,39 @@
         <v>16</v>
       </c>
       <c r="M90" t="s" s="12">
+        <v>16</v>
+      </c>
+      <c r="N90" t="s" s="12">
         <v>16</v>
       </c>
     </row>
     <row r="91" ht="44.05" customHeight="1">
       <c r="B91" t="s" s="12">
-        <v>836</v>
+        <v>930</v>
       </c>
       <c r="C91" t="s" s="12">
-        <v>837</v>
-      </c>
-      <c r="D91" s="15">
+        <v>931</v>
+      </c>
+      <c r="D91" t="s" s="12">
+        <v>932</v>
+      </c>
+      <c r="E91" s="15">
         <v>10</v>
       </c>
-      <c r="E91" t="s" s="12">
-        <v>16</v>
-      </c>
       <c r="F91" t="s" s="12">
         <v>16</v>
       </c>
       <c r="G91" t="s" s="12">
-        <v>838</v>
+        <v>16</v>
       </c>
       <c r="H91" t="s" s="12">
-        <v>839</v>
+        <v>933</v>
       </c>
       <c r="I91" t="s" s="12">
-        <v>17</v>
-      </c>
-      <c r="J91" t="s" s="12">
-        <v>16</v>
+        <v>934</v>
+      </c>
+      <c r="J91" s="15">
+        <v>1.3</v>
       </c>
       <c r="K91" t="s" s="12">
         <v>16</v>
@@ -21183,36 +21766,39 @@
         <v>16</v>
       </c>
       <c r="M91" t="s" s="12">
+        <v>16</v>
+      </c>
+      <c r="N91" t="s" s="12">
         <v>16</v>
       </c>
     </row>
     <row r="92" ht="44.05" customHeight="1">
       <c r="B92" t="s" s="12">
-        <v>840</v>
+        <v>935</v>
       </c>
       <c r="C92" t="s" s="12">
-        <v>841</v>
-      </c>
-      <c r="D92" s="15">
+        <v>936</v>
+      </c>
+      <c r="D92" t="s" s="12">
+        <v>937</v>
+      </c>
+      <c r="E92" s="15">
         <v>10</v>
       </c>
-      <c r="E92" t="s" s="12">
-        <v>16</v>
-      </c>
       <c r="F92" t="s" s="12">
         <v>16</v>
       </c>
       <c r="G92" t="s" s="12">
-        <v>842</v>
+        <v>16</v>
       </c>
       <c r="H92" t="s" s="12">
-        <v>843</v>
+        <v>938</v>
       </c>
       <c r="I92" t="s" s="12">
-        <v>17</v>
-      </c>
-      <c r="J92" t="s" s="12">
-        <v>16</v>
+        <v>939</v>
+      </c>
+      <c r="J92" s="15">
+        <v>1.3</v>
       </c>
       <c r="K92" t="s" s="12">
         <v>16</v>
@@ -21221,36 +21807,39 @@
         <v>16</v>
       </c>
       <c r="M92" t="s" s="12">
+        <v>16</v>
+      </c>
+      <c r="N92" t="s" s="12">
         <v>16</v>
       </c>
     </row>
     <row r="93" ht="44.05" customHeight="1">
       <c r="B93" t="s" s="12">
-        <v>844</v>
+        <v>940</v>
       </c>
       <c r="C93" t="s" s="12">
-        <v>845</v>
-      </c>
-      <c r="D93" s="15">
+        <v>941</v>
+      </c>
+      <c r="D93" t="s" s="12">
+        <v>942</v>
+      </c>
+      <c r="E93" s="15">
         <v>10</v>
       </c>
-      <c r="E93" t="s" s="12">
-        <v>16</v>
-      </c>
       <c r="F93" t="s" s="12">
         <v>16</v>
       </c>
       <c r="G93" t="s" s="12">
-        <v>846</v>
+        <v>16</v>
       </c>
       <c r="H93" t="s" s="12">
-        <v>847</v>
+        <v>943</v>
       </c>
       <c r="I93" t="s" s="12">
-        <v>17</v>
-      </c>
-      <c r="J93" t="s" s="12">
-        <v>16</v>
+        <v>944</v>
+      </c>
+      <c r="J93" s="15">
+        <v>1.3</v>
       </c>
       <c r="K93" t="s" s="12">
         <v>16</v>
@@ -21259,36 +21848,39 @@
         <v>16</v>
       </c>
       <c r="M93" t="s" s="12">
+        <v>16</v>
+      </c>
+      <c r="N93" t="s" s="12">
         <v>16</v>
       </c>
     </row>
     <row r="94" ht="44.05" customHeight="1">
       <c r="B94" t="s" s="12">
-        <v>848</v>
+        <v>945</v>
       </c>
       <c r="C94" t="s" s="12">
-        <v>849</v>
-      </c>
-      <c r="D94" s="15">
+        <v>946</v>
+      </c>
+      <c r="D94" t="s" s="12">
+        <v>947</v>
+      </c>
+      <c r="E94" s="15">
         <v>10</v>
       </c>
-      <c r="E94" t="s" s="12">
-        <v>16</v>
-      </c>
       <c r="F94" t="s" s="12">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G94" t="s" s="12">
-        <v>850</v>
+        <v>17</v>
       </c>
       <c r="H94" t="s" s="12">
-        <v>851</v>
+        <v>948</v>
       </c>
       <c r="I94" t="s" s="12">
-        <v>17</v>
-      </c>
-      <c r="J94" t="s" s="12">
-        <v>16</v>
+        <v>949</v>
+      </c>
+      <c r="J94" s="15">
+        <v>1.3</v>
       </c>
       <c r="K94" t="s" s="12">
         <v>16</v>
@@ -21297,36 +21889,39 @@
         <v>16</v>
       </c>
       <c r="M94" t="s" s="12">
+        <v>16</v>
+      </c>
+      <c r="N94" t="s" s="12">
         <v>16</v>
       </c>
     </row>
     <row r="95" ht="32.05" customHeight="1">
       <c r="B95" t="s" s="12">
-        <v>852</v>
+        <v>950</v>
       </c>
       <c r="C95" t="s" s="12">
-        <v>853</v>
-      </c>
-      <c r="D95" s="15">
+        <v>951</v>
+      </c>
+      <c r="D95" t="s" s="12">
+        <v>952</v>
+      </c>
+      <c r="E95" s="15">
         <v>10</v>
       </c>
-      <c r="E95" t="s" s="12">
-        <v>16</v>
-      </c>
       <c r="F95" t="s" s="12">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G95" t="s" s="12">
-        <v>854</v>
+        <v>17</v>
       </c>
       <c r="H95" t="s" s="12">
-        <v>855</v>
+        <v>953</v>
       </c>
       <c r="I95" t="s" s="12">
-        <v>17</v>
-      </c>
-      <c r="J95" t="s" s="12">
-        <v>16</v>
+        <v>954</v>
+      </c>
+      <c r="J95" s="15">
+        <v>1.3</v>
       </c>
       <c r="K95" t="s" s="12">
         <v>16</v>
@@ -21335,36 +21930,39 @@
         <v>16</v>
       </c>
       <c r="M95" t="s" s="12">
+        <v>16</v>
+      </c>
+      <c r="N95" t="s" s="12">
         <v>16</v>
       </c>
     </row>
     <row r="96" ht="56.05" customHeight="1">
       <c r="B96" t="s" s="12">
-        <v>856</v>
+        <v>955</v>
       </c>
       <c r="C96" t="s" s="12">
-        <v>857</v>
-      </c>
-      <c r="D96" s="15">
+        <v>956</v>
+      </c>
+      <c r="D96" t="s" s="12">
+        <v>957</v>
+      </c>
+      <c r="E96" s="15">
         <v>10</v>
       </c>
-      <c r="E96" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F96" t="s" s="12">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G96" t="s" s="12">
-        <v>858</v>
+        <v>16</v>
       </c>
       <c r="H96" t="s" s="12">
-        <v>859</v>
+        <v>958</v>
       </c>
       <c r="I96" t="s" s="12">
-        <v>17</v>
-      </c>
-      <c r="J96" t="s" s="12">
-        <v>16</v>
+        <v>959</v>
+      </c>
+      <c r="J96" s="15">
+        <v>1.3</v>
       </c>
       <c r="K96" t="s" s="12">
         <v>16</v>
@@ -21373,72 +21971,78 @@
         <v>16</v>
       </c>
       <c r="M96" t="s" s="12">
+        <v>16</v>
+      </c>
+      <c r="N96" t="s" s="12">
         <v>16</v>
       </c>
     </row>
     <row r="97" ht="44.05" customHeight="1">
       <c r="B97" t="s" s="12">
-        <v>860</v>
+        <v>960</v>
       </c>
       <c r="C97" t="s" s="12">
-        <v>861</v>
-      </c>
-      <c r="D97" s="15">
+        <v>961</v>
+      </c>
+      <c r="D97" t="s" s="12">
+        <v>962</v>
+      </c>
+      <c r="E97" s="15">
         <v>10</v>
       </c>
-      <c r="E97" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F97" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G97" t="s" s="12">
-        <v>862</v>
+        <v>17</v>
       </c>
       <c r="H97" t="s" s="12">
-        <v>862</v>
+        <v>963</v>
       </c>
       <c r="I97" t="s" s="12">
-        <v>17</v>
-      </c>
-      <c r="J97" s="14"/>
-      <c r="K97" t="s" s="12">
-        <v>16</v>
-      </c>
+        <v>963</v>
+      </c>
+      <c r="J97" s="15">
+        <v>1.3</v>
+      </c>
+      <c r="K97" s="14"/>
       <c r="L97" t="s" s="12">
         <v>16</v>
       </c>
       <c r="M97" t="s" s="12">
+        <v>16</v>
+      </c>
+      <c r="N97" t="s" s="12">
         <v>16</v>
       </c>
     </row>
     <row r="98" ht="44.05" customHeight="1">
       <c r="B98" t="s" s="12">
-        <v>863</v>
+        <v>964</v>
       </c>
       <c r="C98" t="s" s="12">
-        <v>864</v>
-      </c>
-      <c r="D98" s="15">
+        <v>965</v>
+      </c>
+      <c r="D98" t="s" s="12">
+        <v>966</v>
+      </c>
+      <c r="E98" s="15">
         <v>10</v>
       </c>
-      <c r="E98" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F98" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G98" t="s" s="12">
-        <v>865</v>
+        <v>17</v>
       </c>
       <c r="H98" t="s" s="12">
-        <v>866</v>
+        <v>967</v>
       </c>
       <c r="I98" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="J98" t="s" s="12">
-        <v>16</v>
+        <v>968</v>
+      </c>
+      <c r="J98" s="15">
+        <v>1.3</v>
       </c>
       <c r="K98" t="s" s="12">
         <v>16</v>
@@ -21447,36 +22051,39 @@
         <v>16</v>
       </c>
       <c r="M98" t="s" s="12">
+        <v>16</v>
+      </c>
+      <c r="N98" t="s" s="12">
         <v>16</v>
       </c>
     </row>
     <row r="99" ht="44.05" customHeight="1">
       <c r="B99" t="s" s="12">
-        <v>867</v>
+        <v>969</v>
       </c>
       <c r="C99" t="s" s="12">
-        <v>868</v>
-      </c>
-      <c r="D99" s="15">
+        <v>970</v>
+      </c>
+      <c r="D99" t="s" s="12">
+        <v>971</v>
+      </c>
+      <c r="E99" s="15">
         <v>10</v>
       </c>
-      <c r="E99" t="s" s="12">
-        <v>17</v>
-      </c>
       <c r="F99" t="s" s="12">
         <v>17</v>
       </c>
       <c r="G99" t="s" s="12">
-        <v>869</v>
+        <v>17</v>
       </c>
       <c r="H99" t="s" s="12">
-        <v>870</v>
+        <v>972</v>
       </c>
       <c r="I99" t="s" s="12">
-        <v>16</v>
-      </c>
-      <c r="J99" t="s" s="12">
-        <v>16</v>
+        <v>973</v>
+      </c>
+      <c r="J99" s="15">
+        <v>1.3</v>
       </c>
       <c r="K99" t="s" s="12">
         <v>16</v>
@@ -21485,6 +22092,9 @@
         <v>16</v>
       </c>
       <c r="M99" t="s" s="12">
+        <v>16</v>
+      </c>
+      <c r="N99" t="s" s="12">
         <v>16</v>
       </c>
     </row>
